--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC728C04-F161-4FD1-9DC3-8245BD1E5A8A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1E6B0F-1DE7-416B-B11D-1230B8FB98AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="140" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="129">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -146,12 +146,6 @@
     <t>Heat Sink</t>
   </si>
   <si>
-    <t>HSB20-353525</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/same-sky-formerly-cui-devices/HSB20-353525/14567120</t>
-  </si>
-  <si>
     <t>https://www.digikey.ca/en/products/detail/adafruit-industries-llc/1468/7241459</t>
   </si>
   <si>
@@ -305,12 +299,6 @@
     <t>https://www.digikey.ca/en/products/detail/jst-sales-america-inc/SM04B-GHS-TB/807788</t>
   </si>
   <si>
-    <t>UVR1H101MPD1TD</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/nichicon/UVR1H101MPD1TD/3438549</t>
-  </si>
-  <si>
     <t>EKYC101ELL331MK25S</t>
   </si>
   <si>
@@ -423,6 +411,18 @@
   </si>
   <si>
     <t>*6 out of 5</t>
+  </si>
+  <si>
+    <t>HSB35-272725</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/same-sky-formerly-cui-devices/HSB35-272725/22535724</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C440833.html</t>
+  </si>
+  <si>
+    <t>50YXJ100MT78X11.5</t>
   </si>
 </sst>
 </file>
@@ -458,11 +458,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -816,10 +814,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -834,10 +832,10 @@
         <v/>
       </c>
       <c r="R2" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="U2">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
@@ -854,7 +852,7 @@
         <f>IF(COUNT(C3:D3)=2,D3*C3*IF(ISNUMBER(SEARCH("lcsc", F3)), U$2, 1),"")</f>
         <v>7.21</v>
       </c>
-      <c r="F3" s="2" t="s">
+      <c r="F3" t="s">
         <v>13</v>
       </c>
     </row>
@@ -869,10 +867,10 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -885,7 +883,7 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -920,23 +918,26 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>89</v>
+        <v>128</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
       </c>
       <c r="C8">
-        <v>2</v>
+        <v>0.4</v>
       </c>
       <c r="D8" s="1">
-        <v>0.43</v>
+        <v>0.47</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
-        <v>0.86</v>
+        <v>0.25756000000000001</v>
       </c>
       <c r="F8" t="s">
-        <v>90</v>
+        <v>127</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>96</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
@@ -954,15 +955,15 @@
       </c>
       <c r="E9" s="1">
         <f t="shared" si="1"/>
-        <v>0.46240000000000009</v>
+        <v>0.46580000000000005</v>
       </c>
       <c r="F9" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -971,7 +972,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -984,7 +985,7 @@
         <v>24.88</v>
       </c>
       <c r="F11" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
@@ -1028,10 +1029,10 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B15" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C15">
         <v>0.4</v>
@@ -1041,13 +1042,13 @@
       </c>
       <c r="E15" s="1">
         <f t="shared" si="1"/>
-        <v>0.73440000000000005</v>
+        <v>0.73980000000000012</v>
       </c>
       <c r="F15" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="Q15" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
@@ -1065,10 +1066,10 @@
       </c>
       <c r="E16" s="1">
         <f t="shared" si="1"/>
-        <v>12.512</v>
+        <v>12.603999999999999</v>
       </c>
       <c r="F16" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
@@ -1082,25 +1083,25 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>36</v>
+        <v>125</v>
       </c>
       <c r="C18">
         <v>1</v>
       </c>
       <c r="D18" s="1">
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="E18" s="1">
         <f t="shared" si="1"/>
-        <v>3.3</v>
+        <v>2.96</v>
       </c>
       <c r="F18" t="s">
-        <v>37</v>
+        <v>126</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="C19">
         <v>0.01</v>
@@ -1113,7 +1114,7 @@
         <v>6.9400000000000003E-2</v>
       </c>
       <c r="F19" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
@@ -1127,10 +1128,10 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="C21">
         <v>0.02</v>
@@ -1140,21 +1141,21 @@
       </c>
       <c r="E21" s="1">
         <f t="shared" si="1"/>
-        <v>1.3872000000000002E-2</v>
+        <v>1.3974000000000002E-2</v>
       </c>
       <c r="F21" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="Q21" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B22" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C22">
         <v>0.05</v>
@@ -1164,21 +1165,21 @@
       </c>
       <c r="E22" s="1">
         <f t="shared" si="1"/>
-        <v>7.4800000000000014E-3</v>
+        <v>7.5350000000000018E-3</v>
       </c>
       <c r="F22" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="Q22" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="C23">
         <v>0.02</v>
@@ -1188,13 +1189,13 @@
       </c>
       <c r="E23" s="1">
         <f t="shared" si="1"/>
-        <v>1.6048E-2</v>
+        <v>1.6166E-2</v>
       </c>
       <c r="F23" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="Q23" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
@@ -1208,7 +1209,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -1221,12 +1222,12 @@
         <v>0.9</v>
       </c>
       <c r="F25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -1239,12 +1240,12 @@
         <v>2.86</v>
       </c>
       <c r="F26" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="C27">
         <v>0.4</v>
@@ -1254,18 +1255,18 @@
       </c>
       <c r="E27" s="1">
         <f t="shared" si="1"/>
-        <v>0.26112000000000002</v>
+        <v>0.26304000000000005</v>
       </c>
       <c r="F27" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="Q27" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -1278,12 +1279,12 @@
         <v>0.92</v>
       </c>
       <c r="F28" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B29" t="str">
         <f>TEXT(2.2, "#.#")</f>
@@ -1297,18 +1298,18 @@
       </c>
       <c r="E29" s="1">
         <f t="shared" si="1"/>
-        <v>9.5199999999999989E-3</v>
+        <v>9.5899999999999996E-3</v>
       </c>
       <c r="F29" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="Q29" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="B30" t="str">
         <f>TEXT(3.3, "#.#")</f>
@@ -1322,18 +1323,18 @@
       </c>
       <c r="E30" s="1">
         <f t="shared" si="1"/>
-        <v>2.2848E-2</v>
+        <v>2.3016000000000002E-2</v>
       </c>
       <c r="F30" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="Q30" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="B31" t="str">
         <f>TEXT(1, "#")</f>
@@ -1347,18 +1348,18 @@
       </c>
       <c r="E31" s="1">
         <f t="shared" si="1"/>
-        <v>1.9039999999999998E-2</v>
+        <v>1.9179999999999999E-2</v>
       </c>
       <c r="F31" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="Q31" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
@@ -1370,19 +1371,19 @@
         <v>0.27</v>
       </c>
       <c r="E32" s="1">
-        <f>IF(COUNT(C32:D32)=2,D32*C32*IF(ISNUMBER(SEARCH("lcsc", F32)), U$2, 1),"")</f>
-        <v>1.4688000000000001E-2</v>
+        <f t="shared" ref="E32:E52" si="2">IF(COUNT(C32:D32)=2,D32*C32*IF(ISNUMBER(SEARCH("lcsc", F32)), U$2, 1),"")</f>
+        <v>1.4796000000000002E-2</v>
       </c>
       <c r="F32" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="Q32" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B33" t="s">
         <v>20</v>
@@ -1394,19 +1395,19 @@
         <v>0.15</v>
       </c>
       <c r="E33" s="1">
-        <f>IF(COUNT(C33:D33)=2,D33*C33*IF(ISNUMBER(SEARCH("lcsc", F33)), U$2, 1),"")</f>
-        <v>4.0800000000000003E-2</v>
+        <f t="shared" si="2"/>
+        <v>4.1100000000000005E-2</v>
       </c>
       <c r="F33" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="Q33" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -1418,19 +1419,19 @@
         <v>0.71</v>
       </c>
       <c r="E34" s="1">
-        <f>IF(COUNT(C34:D34)=2,D34*C34*IF(ISNUMBER(SEARCH("lcsc", F34)), U$2, 1),"")</f>
-        <v>1.9311999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.9453999999999999E-2</v>
       </c>
       <c r="F34" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="Q34" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
@@ -1442,19 +1443,19 @@
         <v>0.18</v>
       </c>
       <c r="E35" s="1">
-        <f>IF(COUNT(C35:D35)=2,D35*C35*IF(ISNUMBER(SEARCH("lcsc", F35)), U$2, 1),"")</f>
-        <v>4.8960000000000002E-3</v>
+        <f t="shared" si="2"/>
+        <v>4.9320000000000006E-3</v>
       </c>
       <c r="F35" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="Q35" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B36" t="s">
         <v>28</v>
@@ -1466,22 +1467,22 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E36" s="1">
-        <f>IF(COUNT(C36:D36)=2,D36*C36*IF(ISNUMBER(SEARCH("lcsc", F36)), U$2, 1),"")</f>
-        <v>1.4960000000000003E-2</v>
+        <f t="shared" si="2"/>
+        <v>1.5070000000000004E-2</v>
       </c>
       <c r="F36" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="Q36" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="B37" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C37">
         <v>0.01</v>
@@ -1490,22 +1491,22 @@
         <v>0.14000000000000001</v>
       </c>
       <c r="E37" s="1">
-        <f>IF(COUNT(C37:D37)=2,D37*C37*IF(ISNUMBER(SEARCH("lcsc", F37)), U$2, 1),"")</f>
-        <v>1.9040000000000003E-3</v>
+        <f t="shared" si="2"/>
+        <v>1.9180000000000004E-3</v>
       </c>
       <c r="F37" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="Q37" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B38" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="C38">
         <v>0.12</v>
@@ -1514,19 +1515,19 @@
         <v>0.52</v>
       </c>
       <c r="E38" s="1">
-        <f>IF(COUNT(C38:D38)=2,D38*C38*IF(ISNUMBER(SEARCH("lcsc", F38)), U$2, 1),"")</f>
-        <v>8.4864000000000009E-2</v>
+        <f t="shared" si="2"/>
+        <v>8.5488000000000008E-2</v>
       </c>
       <c r="F38" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="Q38" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1535,19 +1536,19 @@
         <v>0.23</v>
       </c>
       <c r="E39" s="1">
-        <f>IF(COUNT(C39:D39)=2,D39*C39*IF(ISNUMBER(SEARCH("lcsc", F39)), U$2, 1),"")</f>
+        <f t="shared" si="2"/>
         <v>0.23</v>
       </c>
       <c r="F39" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B40" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C40">
         <v>0.08</v>
@@ -1556,19 +1557,19 @@
         <v>0.52</v>
       </c>
       <c r="E40" s="1">
-        <f>IF(COUNT(C40:D40)=2,D40*C40*IF(ISNUMBER(SEARCH("lcsc", F40)), U$2, 1),"")</f>
-        <v>5.6576000000000008E-2</v>
+        <f t="shared" si="2"/>
+        <v>5.6992000000000008E-2</v>
       </c>
       <c r="F40" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="Q40" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="C41">
         <v>1.2</v>
@@ -1577,14 +1578,14 @@
         <v>0.39</v>
       </c>
       <c r="E41" s="1">
-        <f>IF(COUNT(C41:D41)=2,D41*C41*IF(ISNUMBER(SEARCH("lcsc", F41)), U$2, 1),"")</f>
-        <v>0.63648000000000005</v>
+        <f t="shared" si="2"/>
+        <v>0.64116000000000006</v>
       </c>
       <c r="F41" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="Q41" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
@@ -1592,7 +1593,7 @@
         <v>30</v>
       </c>
       <c r="E42" s="1" t="str">
-        <f>IF(COUNT(C42:D42)=2,D42*C42*IF(ISNUMBER(SEARCH("lcsc", F42)), U$2, 1),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -1607,11 +1608,11 @@
         <v>0.67</v>
       </c>
       <c r="E43" s="1">
-        <f>IF(COUNT(C43:D43)=2,D43*C43*IF(ISNUMBER(SEARCH("lcsc", F43)), U$2, 1),"")</f>
-        <v>0.91120000000000012</v>
+        <f t="shared" si="2"/>
+        <v>0.91790000000000016</v>
       </c>
       <c r="F43" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
@@ -1625,14 +1626,14 @@
         <v>0.51</v>
       </c>
       <c r="E44" s="1">
-        <f>IF(COUNT(C44:D44)=2,D44*C44*IF(ISNUMBER(SEARCH("lcsc", F44)), U$2, 1),"")</f>
-        <v>6.9360000000000005E-2</v>
+        <f t="shared" si="2"/>
+        <v>6.9870000000000015E-2</v>
       </c>
       <c r="F44" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="Q44" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
@@ -1649,36 +1650,36 @@
         <v>0.31</v>
       </c>
       <c r="E45" s="1">
-        <f>IF(COUNT(C45:D45)=2,D45*C45*IF(ISNUMBER(SEARCH("lcsc", F45)), U$2, 1),"")</f>
-        <v>2.5295999999999999E-2</v>
+        <f t="shared" si="2"/>
+        <v>2.5482000000000001E-2</v>
       </c>
       <c r="F45" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="Q45" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B46" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="C46" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="E46" s="1" t="str">
-        <f>IF(COUNT(C46:D46)=2,D46*C46*IF(ISNUMBER(SEARCH("lcsc", F46)), U$2, 1),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>66</v>
-      </c>
-      <c r="B47" s="3" t="str">
+        <v>64</v>
+      </c>
+      <c r="B47" t="str">
         <f>TEXT("10", "#")</f>
         <v>10</v>
       </c>
@@ -1689,34 +1690,34 @@
         <v>0.34</v>
       </c>
       <c r="E47" s="1">
-        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
-        <v>9.248000000000001E-3</v>
+        <f t="shared" si="2"/>
+        <v>9.3160000000000014E-3</v>
       </c>
       <c r="F47" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="Q47" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
       </c>
       <c r="C48" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="E48" s="1" t="str">
-        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -1725,25 +1726,25 @@
         <v>0.68</v>
       </c>
       <c r="E49" s="1">
-        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
+        <f t="shared" si="2"/>
         <v>1.36</v>
       </c>
       <c r="F49" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A50" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="E50" s="1" t="str">
-        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A51" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C51">
         <v>2</v>
@@ -1752,16 +1753,16 @@
         <v>0.5</v>
       </c>
       <c r="E51" s="1">
-        <f>IF(COUNT(C51:D51)=2,D51*C51*IF(ISNUMBER(SEARCH("lcsc", F51)), U$2, 1),"")</f>
-        <v>1.36</v>
+        <f t="shared" si="2"/>
+        <v>1.37</v>
       </c>
       <c r="F51" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A52" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="C52">
         <v>2</v>
@@ -1770,11 +1771,11 @@
         <v>0.55000000000000004</v>
       </c>
       <c r="E52" s="1">
-        <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
+        <f t="shared" si="2"/>
         <v>1.1000000000000001</v>
       </c>
       <c r="F52" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -1783,7 +1784,7 @@
       </c>
       <c r="E53" s="1">
         <f>SUM(E2:E52)</f>
-        <v>82.357712000000021</v>
+        <v>81.542539000000005</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B1E6B0F-1DE7-416B-B11D-1230B8FB98AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145EE886-1510-4932-A3A9-7526510BCB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -410,9 +410,6 @@
     <t>https://www.lcsc.com/product-detail/C112305.html</t>
   </si>
   <si>
-    <t>*6 out of 5</t>
-  </si>
-  <si>
     <t>HSB35-272725</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>50YXJ100MT78X11.5</t>
+  </si>
+  <si>
+    <t>*4 out of 5</t>
   </si>
 </sst>
 </file>
@@ -918,7 +918,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -934,7 +934,7 @@
         <v>0.25756000000000001</v>
       </c>
       <c r="F8" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="Q8" t="s">
         <v>96</v>
@@ -1083,7 +1083,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1096,7 +1096,7 @@
         <v>2.96</v>
       </c>
       <c r="F18" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
@@ -1572,20 +1572,20 @@
         <v>85</v>
       </c>
       <c r="C41">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D41" s="1">
         <v>0.39</v>
       </c>
       <c r="E41" s="1">
         <f t="shared" si="2"/>
-        <v>0.64116000000000006</v>
+        <v>0.4274400000000001</v>
       </c>
       <c r="F41" t="s">
         <v>84</v>
       </c>
       <c r="Q41" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E53" s="1">
         <f>SUM(E2:E52)</f>
-        <v>81.542539000000005</v>
+        <v>81.32881900000001</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{145EE886-1510-4932-A3A9-7526510BCB37}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EFD32D-169D-4283-ABFD-94045D03155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -233,9 +233,6 @@
     <t>RC0603FR-0710RL</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C109318.html</t>
-  </si>
-  <si>
     <t>*2 out of 100</t>
   </si>
   <si>
@@ -260,9 +257,6 @@
     <t>https://www.lcsc.com/product-detail/C469659.html</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C863663.html</t>
-  </si>
-  <si>
     <t>RT0603FRE07100KL</t>
   </si>
   <si>
@@ -311,12 +305,6 @@
     <t>GanFET</t>
   </si>
   <si>
-    <t>IGC019S06S1XTMA1</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/infineon-technologies/IGC019S06S1XTMA1/25902301</t>
-  </si>
-  <si>
     <t>ASR-K-3-2.2F</t>
   </si>
   <si>
@@ -423,6 +411,18 @@
   </si>
   <si>
     <t>*4 out of 5</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C706131.html</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/yageo/RT0603FRE0710RL/1075044</t>
+  </si>
+  <si>
+    <t>IGC025S08S1XTMA1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/infineon-technologies/IGC025S08S1XTMA1/25902269</t>
   </si>
 </sst>
 </file>
@@ -814,10 +814,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -832,7 +832,7 @@
         <v/>
       </c>
       <c r="R2" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
       <c r="U2">
         <v>1.37</v>
@@ -867,10 +867,10 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B5" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -883,7 +883,7 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -918,7 +918,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -934,10 +934,10 @@
         <v>0.25756000000000001</v>
       </c>
       <c r="F8" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="Q8" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
@@ -963,7 +963,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -972,20 +972,20 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>91</v>
+        <v>127</v>
       </c>
       <c r="C11">
         <v>4</v>
       </c>
       <c r="D11" s="1">
-        <v>6.22</v>
+        <v>6.63</v>
       </c>
       <c r="E11" s="1">
         <f t="shared" si="1"/>
-        <v>24.88</v>
+        <v>26.52</v>
       </c>
       <c r="F11" t="s">
-        <v>92</v>
+        <v>128</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
@@ -1029,10 +1029,10 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C15">
         <v>0.4</v>
@@ -1045,10 +1045,10 @@
         <v>0.73980000000000012</v>
       </c>
       <c r="F15" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="Q15" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
@@ -1083,7 +1083,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1096,7 +1096,7 @@
         <v>2.96</v>
       </c>
       <c r="F18" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
@@ -1128,10 +1128,10 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="C21">
         <v>0.02</v>
@@ -1144,7 +1144,7 @@
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F21" t="s">
-        <v>74</v>
+        <v>125</v>
       </c>
       <c r="Q21" t="s">
         <v>56</v>
@@ -1152,10 +1152,10 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="C22">
         <v>0.05</v>
@@ -1168,18 +1168,18 @@
         <v>7.5350000000000018E-3</v>
       </c>
       <c r="F22" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="Q22" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="B23" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
       <c r="C23">
         <v>0.02</v>
@@ -1209,7 +1209,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -1222,12 +1222,12 @@
         <v>0.9</v>
       </c>
       <c r="F25" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -1240,12 +1240,12 @@
         <v>2.86</v>
       </c>
       <c r="F26" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="C27">
         <v>0.4</v>
@@ -1258,15 +1258,15 @@
         <v>0.26304000000000005</v>
       </c>
       <c r="F27" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="Q27" t="s">
-        <v>114</v>
+        <v>110</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -1279,12 +1279,12 @@
         <v>0.92</v>
       </c>
       <c r="F28" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="B29" t="str">
         <f>TEXT(2.2, "#.#")</f>
@@ -1301,15 +1301,15 @@
         <v>9.5899999999999996E-3</v>
       </c>
       <c r="F29" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="Q29" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="B30" t="str">
         <f>TEXT(3.3, "#.#")</f>
@@ -1326,7 +1326,7 @@
         <v>2.3016000000000002E-2</v>
       </c>
       <c r="F30" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="Q30" t="s">
         <v>49</v>
@@ -1334,7 +1334,7 @@
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="B31" t="str">
         <f>TEXT(1, "#")</f>
@@ -1351,7 +1351,7 @@
         <v>1.9179999999999999E-2</v>
       </c>
       <c r="F31" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="Q31" t="s">
         <v>49</v>
@@ -1407,7 +1407,7 @@
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -1423,10 +1423,10 @@
         <v>1.9453999999999999E-2</v>
       </c>
       <c r="F34" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="Q34" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
@@ -1455,7 +1455,7 @@
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B36" t="s">
         <v>28</v>
@@ -1471,7 +1471,7 @@
         <v>1.5070000000000004E-2</v>
       </c>
       <c r="F36" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q36" t="s">
         <v>56</v>
@@ -1479,10 +1479,10 @@
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>67</v>
+      </c>
+      <c r="B37" t="s">
         <v>68</v>
-      </c>
-      <c r="B37" t="s">
-        <v>69</v>
       </c>
       <c r="C37">
         <v>0.01</v>
@@ -1495,7 +1495,7 @@
         <v>1.9180000000000004E-3</v>
       </c>
       <c r="F37" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q37" t="s">
         <v>47</v>
@@ -1503,10 +1503,10 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>70</v>
+      </c>
+      <c r="B38" t="s">
         <v>71</v>
-      </c>
-      <c r="B38" t="s">
-        <v>72</v>
       </c>
       <c r="C38">
         <v>0.12</v>
@@ -1519,15 +1519,15 @@
         <v>8.5488000000000008E-2</v>
       </c>
       <c r="F38" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1540,7 +1540,7 @@
         <v>0.23</v>
       </c>
       <c r="F39" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
@@ -1564,12 +1564,12 @@
         <v>61</v>
       </c>
       <c r="Q40" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="C41">
         <v>0.8</v>
@@ -1582,10 +1582,10 @@
         <v>0.4274400000000001</v>
       </c>
       <c r="F41" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="Q41" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
@@ -1668,7 +1668,7 @@
         <v>39</v>
       </c>
       <c r="C46" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E46" s="1" t="str">
         <f t="shared" si="2"/>
@@ -1684,20 +1684,20 @@
         <v>10</v>
       </c>
       <c r="C47">
-        <v>0.02</v>
+        <v>0.2</v>
       </c>
       <c r="D47" s="1">
-        <v>0.34</v>
+        <v>0.15</v>
       </c>
       <c r="E47" s="1">
         <f t="shared" si="2"/>
-        <v>9.3160000000000014E-3</v>
+        <v>0.03</v>
       </c>
       <c r="F47" t="s">
-        <v>65</v>
+        <v>126</v>
       </c>
       <c r="Q47" t="s">
-        <v>66</v>
+        <v>52</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
@@ -1717,7 +1717,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -1730,7 +1730,7 @@
         <v>1.36</v>
       </c>
       <c r="F49" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -1775,7 +1775,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F52" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">
@@ -1784,7 +1784,7 @@
       </c>
       <c r="E53" s="1">
         <f>SUM(E2:E52)</f>
-        <v>81.32881900000001</v>
+        <v>82.989503000000013</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EFD32D-169D-4283-ABFD-94045D03155A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C9A350-D18D-4C26-A3DA-95D4747131B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -182,9 +182,6 @@
     <t>*1 out of 100</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C472799.html</t>
-  </si>
-  <si>
     <t>*4 out of 100</t>
   </si>
   <si>
@@ -423,6 +420,9 @@
   </si>
   <si>
     <t>https://www.digikey.ca/en/products/detail/infineon-technologies/IGC025S08S1XTMA1/25902269</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C472802.html</t>
   </si>
 </sst>
 </file>
@@ -458,9 +458,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -814,10 +815,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>95</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>96</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>97</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -832,7 +833,7 @@
         <v/>
       </c>
       <c r="R2" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="U2">
         <v>1.37</v>
@@ -867,10 +868,10 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>84</v>
+      </c>
+      <c r="B5" t="s">
         <v>85</v>
-      </c>
-      <c r="B5" t="s">
-        <v>86</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -883,7 +884,7 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -918,7 +919,7 @@
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B8" t="s">
         <v>16</v>
@@ -934,10 +935,10 @@
         <v>0.25756000000000001</v>
       </c>
       <c r="F8" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="Q8" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
@@ -958,12 +959,12 @@
         <v>0.46580000000000005</v>
       </c>
       <c r="F9" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E10" s="1" t="str">
         <f t="shared" si="1"/>
@@ -972,7 +973,7 @@
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="C11">
         <v>4</v>
@@ -985,7 +986,7 @@
         <v>26.52</v>
       </c>
       <c r="F11" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
@@ -1029,10 +1030,10 @@
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" t="s">
         <v>89</v>
-      </c>
-      <c r="B15" t="s">
-        <v>90</v>
       </c>
       <c r="C15">
         <v>0.4</v>
@@ -1045,10 +1046,10 @@
         <v>0.73980000000000012</v>
       </c>
       <c r="F15" t="s">
+        <v>90</v>
+      </c>
+      <c r="Q15" t="s">
         <v>91</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>92</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
@@ -1083,7 +1084,7 @@
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="C18">
         <v>1</v>
@@ -1096,7 +1097,7 @@
         <v>2.96</v>
       </c>
       <c r="F18" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
@@ -1128,10 +1129,10 @@
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
+        <v>92</v>
+      </c>
+      <c r="B21" t="s">
         <v>93</v>
-      </c>
-      <c r="B21" t="s">
-        <v>94</v>
       </c>
       <c r="C21">
         <v>0.02</v>
@@ -1144,18 +1145,18 @@
         <v>1.3974000000000002E-2</v>
       </c>
       <c r="F21" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="Q21" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
+        <v>97</v>
+      </c>
+      <c r="B22" t="s">
         <v>98</v>
-      </c>
-      <c r="B22" t="s">
-        <v>99</v>
       </c>
       <c r="C22">
         <v>0.05</v>
@@ -1168,18 +1169,18 @@
         <v>7.5350000000000018E-3</v>
       </c>
       <c r="F22" t="s">
+        <v>99</v>
+      </c>
+      <c r="Q22" t="s">
         <v>100</v>
-      </c>
-      <c r="Q22" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
+        <v>101</v>
+      </c>
+      <c r="B23" t="s">
         <v>102</v>
-      </c>
-      <c r="B23" t="s">
-        <v>103</v>
       </c>
       <c r="C23">
         <v>0.02</v>
@@ -1191,11 +1192,11 @@
         <f t="shared" si="1"/>
         <v>1.6166E-2</v>
       </c>
-      <c r="F23" t="s">
-        <v>48</v>
+      <c r="F23" s="2" t="s">
+        <v>128</v>
       </c>
       <c r="Q23" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
@@ -1209,7 +1210,7 @@
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="C25">
         <v>2</v>
@@ -1222,12 +1223,12 @@
         <v>0.9</v>
       </c>
       <c r="F25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C26">
         <v>2</v>
@@ -1240,12 +1241,12 @@
         <v>2.86</v>
       </c>
       <c r="F26" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C27">
         <v>0.4</v>
@@ -1258,15 +1259,15 @@
         <v>0.26304000000000005</v>
       </c>
       <c r="F27" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="Q27" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C28">
         <v>4</v>
@@ -1279,12 +1280,12 @@
         <v>0.92</v>
       </c>
       <c r="F28" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="B29" t="str">
         <f>TEXT(2.2, "#.#")</f>
@@ -1301,15 +1302,15 @@
         <v>9.5899999999999996E-3</v>
       </c>
       <c r="F29" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="Q29" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B30" t="str">
         <f>TEXT(3.3, "#.#")</f>
@@ -1326,15 +1327,15 @@
         <v>2.3016000000000002E-2</v>
       </c>
       <c r="F30" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="Q30" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B31" t="str">
         <f>TEXT(1, "#")</f>
@@ -1351,15 +1352,15 @@
         <v>1.9179999999999999E-2</v>
       </c>
       <c r="F31" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="Q31" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B32" t="s">
         <v>19</v>
@@ -1375,15 +1376,15 @@
         <v>1.4796000000000002E-2</v>
       </c>
       <c r="F32" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="Q32" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="B33" t="s">
         <v>20</v>
@@ -1399,15 +1400,15 @@
         <v>4.1100000000000005E-2</v>
       </c>
       <c r="F33" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q33" t="s">
         <v>51</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>52</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="B34" t="s">
         <v>21</v>
@@ -1423,15 +1424,15 @@
         <v>1.9453999999999999E-2</v>
       </c>
       <c r="F34" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="Q34" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B35" t="s">
         <v>23</v>
@@ -1447,15 +1448,15 @@
         <v>4.9320000000000006E-3</v>
       </c>
       <c r="F35" t="s">
+        <v>54</v>
+      </c>
+      <c r="Q35" t="s">
         <v>55</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>56</v>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="B36" t="s">
         <v>28</v>
@@ -1471,18 +1472,18 @@
         <v>1.5070000000000004E-2</v>
       </c>
       <c r="F36" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q36" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
+        <v>66</v>
+      </c>
+      <c r="B37" t="s">
         <v>67</v>
-      </c>
-      <c r="B37" t="s">
-        <v>68</v>
       </c>
       <c r="C37">
         <v>0.01</v>
@@ -1495,7 +1496,7 @@
         <v>1.9180000000000004E-3</v>
       </c>
       <c r="F37" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q37" t="s">
         <v>47</v>
@@ -1503,10 +1504,10 @@
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
+        <v>69</v>
+      </c>
+      <c r="B38" t="s">
         <v>70</v>
-      </c>
-      <c r="B38" t="s">
-        <v>71</v>
       </c>
       <c r="C38">
         <v>0.12</v>
@@ -1519,15 +1520,15 @@
         <v>8.5488000000000008E-2</v>
       </c>
       <c r="F38" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Q38" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="C39">
         <v>1</v>
@@ -1540,7 +1541,7 @@
         <v>0.23</v>
       </c>
       <c r="F39" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
@@ -1561,15 +1562,15 @@
         <v>5.6992000000000008E-2</v>
       </c>
       <c r="F40" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="Q40" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C41">
         <v>0.8</v>
@@ -1582,10 +1583,10 @@
         <v>0.4274400000000001</v>
       </c>
       <c r="F41" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="Q41" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
@@ -1630,10 +1631,10 @@
         <v>6.9870000000000015E-2</v>
       </c>
       <c r="F44" t="s">
+        <v>57</v>
+      </c>
+      <c r="Q44" t="s">
         <v>58</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
@@ -1654,10 +1655,10 @@
         <v>2.5482000000000001E-2</v>
       </c>
       <c r="F45" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="Q45" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
@@ -1668,7 +1669,7 @@
         <v>39</v>
       </c>
       <c r="C46" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="E46" s="1" t="str">
         <f t="shared" si="2"/>
@@ -1677,7 +1678,7 @@
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="B47" t="str">
         <f>TEXT("10", "#")</f>
@@ -1694,15 +1695,15 @@
         <v>0.03</v>
       </c>
       <c r="F47" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="Q47" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="B48" t="s">
         <v>19</v>
@@ -1717,7 +1718,7 @@
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.35">
       <c r="A49" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="C49">
         <v>2</v>
@@ -1730,7 +1731,7 @@
         <v>1.36</v>
       </c>
       <c r="F49" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.35">
@@ -1775,7 +1776,7 @@
         <v>1.1000000000000001</v>
       </c>
       <c r="F52" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.35">

--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5C9A350-D18D-4C26-A3DA-95D4747131B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4796AFC8-5DC9-4F86-83AE-D524F6B81D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="141" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="140">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -65,21 +65,9 @@
     <t>Inductor</t>
   </si>
   <si>
-    <t>ER26A3DC-100K</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/bourns-inc/ER26A3DC-100K/27574578</t>
-  </si>
-  <si>
     <t>Buck Controller</t>
   </si>
   <si>
-    <t>LM5143RHAR</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/texas-instruments/LM5143RHAR/16341524</t>
-  </si>
-  <si>
     <t>Value</t>
   </si>
   <si>
@@ -128,9 +116,6 @@
     <t>INA226AIDGSR</t>
   </si>
   <si>
-    <t>Telemetry + LDO</t>
-  </si>
-  <si>
     <t>TLV74033PDBVR</t>
   </si>
   <si>
@@ -179,36 +164,18 @@
     <t>https://www.lcsc.com/product-detail/C49851.html</t>
   </si>
   <si>
-    <t>*1 out of 100</t>
-  </si>
-  <si>
     <t>*4 out of 100</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C1591.html</t>
-  </si>
-  <si>
     <t>https://www.lcsc.com/product-detail/C19110.html</t>
   </si>
   <si>
-    <t>*2 out of 10</t>
-  </si>
-  <si>
     <t>CL21B225KAFNNNE</t>
   </si>
   <si>
-    <t>CL10B103KBANNNC</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C1589.html</t>
-  </si>
-  <si>
     <t>*1 out of 50</t>
   </si>
   <si>
-    <t>CL10B104KB8NNNC</t>
-  </si>
-  <si>
     <t>https://www.lcsc.com/product-detail/C3743587.html</t>
   </si>
   <si>
@@ -224,9 +191,6 @@
     <t>https://www.lcsc.com/product-detail/C138687.html</t>
   </si>
   <si>
-    <t>*3 out of 50</t>
-  </si>
-  <si>
     <t>RC0603FR-0710RL</t>
   </si>
   <si>
@@ -236,15 +200,9 @@
     <t>https://www.lcsc.com/product-detail/C728638.html</t>
   </si>
   <si>
-    <t>RC0603FR-07390KL</t>
-  </si>
-  <si>
     <t>390k</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C137735.html</t>
-  </si>
-  <si>
     <t>RT0603FRE0710KL</t>
   </si>
   <si>
@@ -287,9 +245,6 @@
     <t>RH-5001</t>
   </si>
   <si>
-    <t>https://www.digikey.ca/en/products/detail/jst-sales-america-inc/SM04B-GHS-TB/807788</t>
-  </si>
-  <si>
     <t>EKYC101ELL331MK25S</t>
   </si>
   <si>
@@ -299,9 +254,6 @@
     <t>https://www.digikey.ca/en/products/detail/chemi-con/EKYC101ELL331MK25S/26120648</t>
   </si>
   <si>
-    <t>GanFET</t>
-  </si>
-  <si>
     <t>ASR-K-3-2.2F</t>
   </si>
   <si>
@@ -314,12 +266,6 @@
     <t>*2 out of 5</t>
   </si>
   <si>
-    <t>RT0603FRE0718KL</t>
-  </si>
-  <si>
-    <t>18k</t>
-  </si>
-  <si>
     <t>USD to CAD Conversion Rate</t>
   </si>
   <si>
@@ -329,51 +275,9 @@
     <t>Sum (CAD)</t>
   </si>
   <si>
-    <t>CL10B332KB8NNNC</t>
-  </si>
-  <si>
-    <t>3.3nF</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C1613.html</t>
-  </si>
-  <si>
-    <t>*1 out of 20</t>
-  </si>
-  <si>
-    <t>CL10C820JB81PNC</t>
-  </si>
-  <si>
-    <t>82pF</t>
-  </si>
-  <si>
-    <t>V2PM10L-M3/H</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/vishay-general-semiconductor-diodes-division/V2PM10L-M3-H/10638928</t>
-  </si>
-  <si>
-    <t>MBR15H120PC-AU</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/panjit-international-inc/MBR15H120PC-AU-R2-007A1/21187249</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C146335.html</t>
-  </si>
-  <si>
-    <t>CUS10S30,H3F</t>
-  </si>
-  <si>
     <t>*4 out of 10</t>
   </si>
   <si>
-    <t>PLZ5V1C-G3/H</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/vishay-general-semiconductor-diodes-division/PLZ5V1C-G3-H/7594405</t>
-  </si>
-  <si>
     <t>*6 out of 50</t>
   </si>
   <si>
@@ -383,12 +287,6 @@
     <t>https://www.lcsc.com/product-detail/C112307.html</t>
   </si>
   <si>
-    <t>RC0603FR-073R3L</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C137725.html</t>
-  </si>
-  <si>
     <t>RC0603FR-071RL</t>
   </si>
   <si>
@@ -401,28 +299,163 @@
     <t>https://www.digikey.ca/en/products/detail/same-sky-formerly-cui-devices/HSB35-272725/22535724</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C440833.html</t>
-  </si>
-  <si>
-    <t>50YXJ100MT78X11.5</t>
-  </si>
-  <si>
-    <t>*4 out of 5</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C706131.html</t>
-  </si>
-  <si>
-    <t>https://www.digikey.ca/en/products/detail/yageo/RT0603FRE0710RL/1075044</t>
-  </si>
-  <si>
     <t>IGC025S08S1XTMA1</t>
   </si>
   <si>
     <t>https://www.digikey.ca/en/products/detail/infineon-technologies/IGC025S08S1XTMA1/25902269</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C472802.html</t>
+    <t>LM5143QRHARQ1</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C5219258.html</t>
+  </si>
+  <si>
+    <t>RPF0811101M050K</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/kyocera-avx/RPF0811101M050K/20096773</t>
+  </si>
+  <si>
+    <t>CL10B104KC8NNNC</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C15725.html</t>
+  </si>
+  <si>
+    <t>Tallied Above (2x)</t>
+  </si>
+  <si>
+    <t>CL10B103KC8NNNC</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C84709.html</t>
+  </si>
+  <si>
+    <t>*5 out of 100</t>
+  </si>
+  <si>
+    <t>GanFET + Driver</t>
+  </si>
+  <si>
+    <t>LM5113QDPRRQ1</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/texas-instruments/LM5113QDPRRQ1/7034938</t>
+  </si>
+  <si>
+    <t>RC0603FR-071KL</t>
+  </si>
+  <si>
+    <t>1k</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C22548.html</t>
+  </si>
+  <si>
+    <t>CL10C220JB8NNNC</t>
+  </si>
+  <si>
+    <t>22pF</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C1653.html</t>
+  </si>
+  <si>
+    <t>BAT46JFILM</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C111205.html</t>
+  </si>
+  <si>
+    <t>RC0603FR-07100RL</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C105588.html</t>
+  </si>
+  <si>
+    <t>LDOs</t>
+  </si>
+  <si>
+    <t>AP7387-50FDC-7</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/diodes-incorporated/AP7387-50FDC-7/17874785</t>
+  </si>
+  <si>
+    <t>CPQ2620H-100M</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C41347719.html</t>
+  </si>
+  <si>
+    <t>RT0603FRE0712KL</t>
+  </si>
+  <si>
+    <t>12k</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C136933.html</t>
+  </si>
+  <si>
+    <t>GRM1885C1H562JA01D</t>
+  </si>
+  <si>
+    <t>5.6nF</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C440183.html</t>
+  </si>
+  <si>
+    <t>CL10C121JB8NNNC</t>
+  </si>
+  <si>
+    <t>120pF</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C18438.html</t>
+  </si>
+  <si>
+    <t>*12 out of 50</t>
+  </si>
+  <si>
+    <t>*2 out of 50</t>
+  </si>
+  <si>
+    <t>Telemetry</t>
+  </si>
+  <si>
+    <t>Switch</t>
+  </si>
+  <si>
+    <t>SLW-865144-2A-N-SMT-TR</t>
+  </si>
+  <si>
+    <t>https://www.digikey.ca/en/products/detail/same-sky-formerly-cui-devices/SLW-865144-2A-N-SMT-TR/24399296</t>
+  </si>
+  <si>
+    <t>XT60PW-M</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C98732.html</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C189895.html</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C109318.html</t>
+  </si>
+  <si>
+    <t>RT0603FRE07390KL</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C863775.html</t>
+  </si>
+  <si>
+    <t>*3 out of 10</t>
+  </si>
+  <si>
+    <t>*6 out of 5</t>
   </si>
 </sst>
 </file>
@@ -458,10 +491,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -796,7 +828,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E459BF-586A-4F4B-931A-B6F36BAD946F}">
-  <dimension ref="A1:U53"/>
+  <dimension ref="A1:U66"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.453125" customWidth="1"/>
@@ -809,16 +841,16 @@
         <v>1</v>
       </c>
       <c r="B1" t="s">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="C1" t="s">
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>95</v>
+        <v>77</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>96</v>
+        <v>78</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -826,14 +858,14 @@
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="E2" s="1" t="str">
         <f t="shared" ref="E2" si="0">IF(COUNT(C2:D2)=2,D2*C2,"")</f>
         <v/>
       </c>
       <c r="R2" t="s">
-        <v>94</v>
+        <v>76</v>
       </c>
       <c r="U2">
         <v>1.37</v>
@@ -841,20 +873,20 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>12</v>
+        <v>89</v>
       </c>
       <c r="C3">
         <v>1</v>
       </c>
       <c r="D3" s="1">
-        <v>7.21</v>
+        <v>3.72</v>
       </c>
       <c r="E3" s="1">
         <f>IF(COUNT(C3:D3)=2,D3*C3*IF(ISNUMBER(SEARCH("lcsc", F3)), U$2, 1),"")</f>
-        <v>7.21</v>
+        <v>5.0964000000000009</v>
       </c>
       <c r="F3" t="s">
-        <v>13</v>
+        <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -862,16 +894,16 @@
         <v>0</v>
       </c>
       <c r="E4" s="1" t="str">
-        <f t="shared" ref="E4:E31" si="1">IF(COUNT(C4:D4)=2,D4*C4*IF(ISNUMBER(SEARCH("lcsc", F4)), U$2, 1),"")</f>
+        <f t="shared" ref="E4:E8" si="1">IF(COUNT(C4:D4)=2,D4*C4*IF(ISNUMBER(SEARCH("lcsc", F4)), U$2, 1),"")</f>
         <v/>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>84</v>
+        <v>69</v>
       </c>
       <c r="B5" t="s">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -884,7 +916,7 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>86</v>
+        <v>71</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -892,17 +924,17 @@
         <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="C6">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="D6" s="1">
-        <v>0.65</v>
+        <v>0.69</v>
       </c>
       <c r="E6" s="1">
         <f t="shared" si="1"/>
-        <v>2.6</v>
+        <v>5.52</v>
       </c>
       <c r="F6" t="s">
         <v>5</v>
@@ -910,882 +942,1059 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
-      </c>
-      <c r="E7" s="1" t="str">
+        <v>93</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="C7">
+        <v>0.24</v>
+      </c>
+      <c r="D7" s="1">
+        <v>0.33</v>
+      </c>
+      <c r="E7" s="1">
         <f t="shared" si="1"/>
-        <v/>
+        <v>0.10850400000000002</v>
+      </c>
+      <c r="F7" t="s">
+        <v>94</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>126</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>122</v>
+        <v>96</v>
       </c>
       <c r="B8" t="s">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="C8">
-        <v>0.4</v>
+        <v>0.05</v>
       </c>
       <c r="D8" s="1">
-        <v>0.47</v>
+        <v>0.63</v>
       </c>
       <c r="E8" s="1">
         <f t="shared" si="1"/>
-        <v>0.25756000000000001</v>
+        <v>4.3155000000000006E-2</v>
       </c>
       <c r="F8" t="s">
-        <v>121</v>
+        <v>97</v>
       </c>
       <c r="Q8" t="s">
-        <v>91</v>
+        <v>98</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>7</v>
-      </c>
-      <c r="B9" t="s">
-        <v>17</v>
-      </c>
-      <c r="C9">
-        <v>2</v>
-      </c>
-      <c r="D9" s="1">
-        <v>0.17</v>
-      </c>
-      <c r="E9" s="1">
-        <f t="shared" si="1"/>
-        <v>0.46580000000000005</v>
-      </c>
-      <c r="F9" t="s">
-        <v>61</v>
+        <v>6</v>
+      </c>
+      <c r="E9" s="1" t="str">
+        <f>IF(COUNT(C9:D9)=2,D9*C9*IF(ISNUMBER(SEARCH("lcsc", F9)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>91</v>
+      </c>
+      <c r="B10" t="s">
+        <v>12</v>
+      </c>
+      <c r="C10">
+        <v>2</v>
+      </c>
+      <c r="D10" s="1">
+        <v>1.46</v>
+      </c>
+      <c r="E10" s="1">
+        <f>IF(COUNT(C10:D10)=2,D10*C10*IF(ISNUMBER(SEARCH("lcsc", F10)), U$2, 1),"")</f>
+        <v>2.92</v>
+      </c>
+      <c r="F10" t="s">
+        <v>92</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>126</v>
+        <v>7</v>
+      </c>
+      <c r="B11" t="s">
+        <v>13</v>
       </c>
       <c r="C11">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D11" s="1">
-        <v>6.63</v>
+        <v>0.17</v>
       </c>
       <c r="E11" s="1">
-        <f t="shared" si="1"/>
-        <v>26.52</v>
+        <f>IF(COUNT(C11:D11)=2,D11*C11*IF(ISNUMBER(SEARCH("lcsc", F11)), U$2, 1),"")</f>
+        <v>1.1645000000000003</v>
       </c>
       <c r="F11" t="s">
-        <v>127</v>
+        <v>50</v>
       </c>
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>8</v>
-      </c>
-      <c r="E12" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>93</v>
+      </c>
+      <c r="B12" t="s">
+        <v>15</v>
+      </c>
+      <c r="C12" t="s">
+        <v>95</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" t="s">
-        <v>18</v>
-      </c>
-      <c r="C13">
-        <v>2</v>
-      </c>
-      <c r="D13" s="1">
-        <v>5.54</v>
-      </c>
-      <c r="E13" s="1">
-        <f t="shared" si="1"/>
-        <v>11.08</v>
-      </c>
-      <c r="F13" t="s">
-        <v>10</v>
+        <v>99</v>
+      </c>
+      <c r="E13" s="1" t="str">
+        <f>IF(COUNT(C13:D13)=2,D13*C13*IF(ISNUMBER(SEARCH("lcsc", F13)), U$2, 1),"")</f>
+        <v/>
       </c>
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>25</v>
-      </c>
-      <c r="E14" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>87</v>
+      </c>
+      <c r="C14">
+        <v>4</v>
+      </c>
+      <c r="D14" s="1">
+        <v>6.62</v>
+      </c>
+      <c r="E14" s="1">
+        <f>IF(COUNT(C14:D14)=2,D14*C14*IF(ISNUMBER(SEARCH("lcsc", F14)), U$2, 1),"")</f>
+        <v>26.48</v>
+      </c>
+      <c r="F14" t="s">
+        <v>88</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>88</v>
-      </c>
-      <c r="B15" t="s">
-        <v>89</v>
+        <v>100</v>
       </c>
       <c r="C15">
-        <v>0.4</v>
+        <v>2</v>
       </c>
       <c r="D15" s="1">
-        <v>1.35</v>
+        <v>6.79</v>
       </c>
       <c r="E15" s="1">
-        <f t="shared" si="1"/>
-        <v>0.73980000000000012</v>
+        <f t="shared" ref="E15:E21" si="2">IF(COUNT(C15:D15)=2,D15*C15*IF(ISNUMBER(SEARCH("lcsc", F15)), U$2, 1),"")</f>
+        <v>13.58</v>
       </c>
       <c r="F15" t="s">
-        <v>90</v>
-      </c>
-      <c r="Q15" t="s">
-        <v>91</v>
+        <v>101</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>26</v>
+        <v>102</v>
       </c>
       <c r="B16" t="s">
-        <v>27</v>
+        <v>103</v>
       </c>
       <c r="C16">
-        <v>4</v>
+        <v>0.04</v>
       </c>
       <c r="D16" s="1">
-        <v>2.2999999999999998</v>
+        <v>0.13</v>
       </c>
       <c r="E16" s="1">
-        <f t="shared" si="1"/>
-        <v>12.603999999999999</v>
+        <f t="shared" si="2"/>
+        <v>7.124000000000001E-3</v>
       </c>
       <c r="F16" t="s">
-        <v>45</v>
+        <v>104</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>35</v>
-      </c>
-      <c r="E17" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>105</v>
+      </c>
+      <c r="B17" t="s">
+        <v>106</v>
+      </c>
+      <c r="C17">
+        <v>0.04</v>
+      </c>
+      <c r="D17" s="1">
+        <v>0.45</v>
+      </c>
+      <c r="E17" s="1">
+        <f t="shared" si="2"/>
+        <v>2.4660000000000005E-2</v>
+      </c>
+      <c r="F17" t="s">
+        <v>107</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>42</v>
       </c>
     </row>
     <row r="18" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A18" t="s">
-        <v>119</v>
+        <v>27</v>
+      </c>
+      <c r="B18" t="s">
+        <v>28</v>
       </c>
       <c r="C18">
-        <v>1</v>
+        <v>0.12</v>
       </c>
       <c r="D18" s="1">
-        <v>2.96</v>
+        <v>0.32</v>
       </c>
       <c r="E18" s="1">
-        <f t="shared" si="1"/>
-        <v>2.96</v>
+        <f t="shared" si="2"/>
+        <v>5.2608000000000002E-2</v>
       </c>
       <c r="F18" t="s">
-        <v>120</v>
+        <v>48</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>37</v>
+        <v>108</v>
       </c>
       <c r="C19">
-        <v>0.01</v>
+        <v>0.4</v>
       </c>
       <c r="D19" s="1">
-        <v>6.94</v>
+        <v>0.71</v>
       </c>
       <c r="E19" s="1">
-        <f t="shared" si="1"/>
-        <v>6.9400000000000003E-2</v>
+        <f t="shared" si="2"/>
+        <v>0.38907999999999998</v>
       </c>
       <c r="F19" t="s">
-        <v>36</v>
+        <v>109</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>79</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="1" t="str">
-        <f t="shared" si="1"/>
-        <v/>
+        <v>110</v>
+      </c>
+      <c r="B20" t="str">
+        <f>TEXT("100", "#")</f>
+        <v>100</v>
+      </c>
+      <c r="C20">
+        <v>0.02</v>
+      </c>
+      <c r="D20" s="1">
+        <v>0.13</v>
+      </c>
+      <c r="E20" s="1">
+        <f t="shared" si="2"/>
+        <v>3.5620000000000005E-3</v>
+      </c>
+      <c r="F20" t="s">
+        <v>111</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>52</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="B21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C21">
-        <v>0.02</v>
-      </c>
-      <c r="D21" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="E21" s="1">
-        <f t="shared" si="1"/>
-        <v>1.3974000000000002E-2</v>
-      </c>
-      <c r="F21" t="s">
-        <v>124</v>
-      </c>
-      <c r="Q21" t="s">
-        <v>55</v>
+        <v>15</v>
+      </c>
+      <c r="C21" t="s">
+        <v>95</v>
+      </c>
+      <c r="E21" s="1" t="str">
+        <f t="shared" si="2"/>
+        <v/>
       </c>
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>97</v>
-      </c>
-      <c r="B22" t="s">
-        <v>98</v>
+        <v>81</v>
+      </c>
+      <c r="B22" t="str">
+        <f>TEXT(2.2, "#.#")</f>
+        <v>2.2</v>
       </c>
       <c r="C22">
-        <v>0.05</v>
+        <v>0.04</v>
       </c>
       <c r="D22" s="1">
-        <v>0.11</v>
+        <v>0.37</v>
       </c>
       <c r="E22" s="1">
-        <f t="shared" si="1"/>
-        <v>7.5350000000000018E-3</v>
+        <f>IF(COUNT(C22:D22)=2,D22*C22*IF(ISNUMBER(SEARCH("lcsc", F22)), U$2, 1),"")</f>
+        <v>2.0276000000000002E-2</v>
       </c>
       <c r="F22" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="Q22" t="s">
-        <v>100</v>
+        <v>42</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>101</v>
-      </c>
-      <c r="B23" t="s">
-        <v>102</v>
+        <v>83</v>
+      </c>
+      <c r="B23" t="str">
+        <f>TEXT(1, "#")</f>
+        <v>1</v>
       </c>
       <c r="C23">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D23" s="1">
-        <v>0.59</v>
+        <v>0.35</v>
       </c>
       <c r="E23" s="1">
-        <f t="shared" si="1"/>
-        <v>1.6166E-2</v>
-      </c>
-      <c r="F23" s="2" t="s">
-        <v>128</v>
+        <f>IF(COUNT(C23:D23)=2,D23*C23*IF(ISNUMBER(SEARCH("lcsc", F23)), U$2, 1),"")</f>
+        <v>1.9179999999999999E-2</v>
+      </c>
+      <c r="F23" t="s">
+        <v>84</v>
       </c>
       <c r="Q23" t="s">
-        <v>55</v>
+        <v>42</v>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>24</v>
+        <v>112</v>
       </c>
       <c r="E24" s="1" t="str">
-        <f t="shared" si="1"/>
+        <f t="shared" ref="E24:E27" si="3">IF(COUNT(C24:D24)=2,D24*C24*IF(ISNUMBER(SEARCH("lcsc", F24)), U$2, 1),"")</f>
         <v/>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>103</v>
+        <v>113</v>
       </c>
       <c r="C25">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D25" s="1">
-        <v>0.45</v>
+        <v>0.75</v>
       </c>
       <c r="E25" s="1">
-        <f t="shared" si="1"/>
-        <v>0.9</v>
+        <f t="shared" si="3"/>
+        <v>0.75</v>
       </c>
       <c r="F25" t="s">
-        <v>104</v>
+        <v>114</v>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>105</v>
-      </c>
-      <c r="C26">
-        <v>2</v>
-      </c>
-      <c r="D26" s="1">
-        <v>1.43</v>
-      </c>
-      <c r="E26" s="1">
-        <f t="shared" si="1"/>
-        <v>2.86</v>
-      </c>
-      <c r="F26" t="s">
-        <v>106</v>
+        <v>27</v>
+      </c>
+      <c r="B26" t="s">
+        <v>28</v>
+      </c>
+      <c r="C26" t="s">
+        <v>66</v>
+      </c>
+      <c r="E26" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>108</v>
-      </c>
-      <c r="C27">
-        <v>0.4</v>
-      </c>
-      <c r="D27" s="1">
-        <v>0.48</v>
-      </c>
-      <c r="E27" s="1">
-        <f t="shared" si="1"/>
-        <v>0.26304000000000005</v>
-      </c>
-      <c r="F27" t="s">
-        <v>107</v>
-      </c>
-      <c r="Q27" t="s">
-        <v>109</v>
+        <v>7</v>
+      </c>
+      <c r="B27" t="s">
+        <v>13</v>
+      </c>
+      <c r="C27" t="s">
+        <v>35</v>
+      </c>
+      <c r="E27" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="28" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A28" t="s">
-        <v>110</v>
+        <v>26</v>
       </c>
       <c r="C28">
-        <v>4</v>
+        <v>0.1</v>
       </c>
       <c r="D28" s="1">
-        <v>0.23</v>
+        <v>0.51</v>
       </c>
       <c r="E28" s="1">
-        <f t="shared" si="1"/>
-        <v>0.92</v>
+        <f t="shared" ref="E28:E42" si="4">IF(COUNT(C28:D28)=2,D28*C28*IF(ISNUMBER(SEARCH("lcsc", F28)), U$2, 1),"")</f>
+        <v>6.9870000000000015E-2</v>
       </c>
       <c r="F28" t="s">
-        <v>111</v>
+        <v>46</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="29" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A29" t="s">
-        <v>113</v>
-      </c>
-      <c r="B29" t="str">
-        <f>TEXT(2.2, "#.#")</f>
-        <v>2.2</v>
+        <v>55</v>
+      </c>
+      <c r="B29" t="s">
+        <v>56</v>
       </c>
       <c r="C29">
-        <v>0.02</v>
+        <v>0.04</v>
       </c>
       <c r="D29" s="1">
-        <v>0.35</v>
+        <v>0.52</v>
       </c>
       <c r="E29" s="1">
-        <f t="shared" si="1"/>
-        <v>9.5899999999999996E-3</v>
+        <f t="shared" si="4"/>
+        <v>2.8496000000000004E-2</v>
       </c>
       <c r="F29" t="s">
-        <v>114</v>
+        <v>57</v>
       </c>
       <c r="Q29" t="s">
-        <v>64</v>
+        <v>127</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>115</v>
-      </c>
-      <c r="B30" t="str">
-        <f>TEXT(3.3, "#.#")</f>
-        <v>3.3</v>
-      </c>
-      <c r="C30">
-        <v>0.04</v>
-      </c>
-      <c r="D30" s="1">
-        <v>0.42</v>
-      </c>
-      <c r="E30" s="1">
-        <f t="shared" si="1"/>
-        <v>2.3016000000000002E-2</v>
-      </c>
-      <c r="F30" t="s">
-        <v>116</v>
-      </c>
-      <c r="Q30" t="s">
-        <v>48</v>
+        <v>8</v>
+      </c>
+      <c r="E30" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="31" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A31" t="s">
-        <v>117</v>
-      </c>
-      <c r="B31" t="str">
-        <f>TEXT(1, "#")</f>
-        <v>1</v>
+        <v>115</v>
+      </c>
+      <c r="B31" t="s">
+        <v>14</v>
       </c>
       <c r="C31">
-        <v>0.04</v>
+        <v>2</v>
       </c>
       <c r="D31" s="1">
-        <v>0.35</v>
+        <v>2.99</v>
       </c>
       <c r="E31" s="1">
-        <f t="shared" si="1"/>
-        <v>1.9179999999999999E-2</v>
+        <f t="shared" si="4"/>
+        <v>8.1926000000000005</v>
       </c>
       <c r="F31" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q31" t="s">
-        <v>48</v>
+        <v>116</v>
       </c>
     </row>
     <row r="32" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A32" t="s">
-        <v>56</v>
-      </c>
-      <c r="B32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C32">
-        <v>0.04</v>
-      </c>
-      <c r="D32" s="1">
-        <v>0.27</v>
-      </c>
-      <c r="E32" s="1">
-        <f t="shared" ref="E32:E52" si="2">IF(COUNT(C32:D32)=2,D32*C32*IF(ISNUMBER(SEARCH("lcsc", F32)), U$2, 1),"")</f>
-        <v>1.4796000000000002E-2</v>
-      </c>
-      <c r="F32" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q32" t="s">
-        <v>48</v>
+        <v>21</v>
+      </c>
+      <c r="E32" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="33" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A33" t="s">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="B33" t="s">
-        <v>20</v>
+        <v>73</v>
       </c>
       <c r="C33">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="D33" s="1">
-        <v>0.15</v>
+        <v>1.35</v>
       </c>
       <c r="E33" s="1">
-        <f t="shared" si="2"/>
-        <v>4.1100000000000005E-2</v>
+        <f t="shared" si="4"/>
+        <v>0.73980000000000012</v>
       </c>
       <c r="F33" t="s">
-        <v>50</v>
+        <v>74</v>
       </c>
       <c r="Q33" t="s">
-        <v>51</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A34" t="s">
-        <v>75</v>
+        <v>22</v>
       </c>
       <c r="B34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C34">
-        <v>0.02</v>
+        <v>4</v>
       </c>
       <c r="D34" s="1">
-        <v>0.71</v>
+        <v>3.13</v>
       </c>
       <c r="E34" s="1">
-        <f t="shared" si="2"/>
-        <v>1.9453999999999999E-2</v>
+        <f t="shared" si="4"/>
+        <v>17.1524</v>
       </c>
       <c r="F34" t="s">
-        <v>76</v>
-      </c>
-      <c r="Q34" t="s">
-        <v>64</v>
+        <v>40</v>
       </c>
     </row>
     <row r="35" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A35" t="s">
-        <v>53</v>
-      </c>
-      <c r="B35" t="s">
-        <v>23</v>
-      </c>
-      <c r="C35">
-        <v>0.02</v>
-      </c>
-      <c r="D35" s="1">
-        <v>0.18</v>
-      </c>
-      <c r="E35" s="1">
-        <f t="shared" si="2"/>
-        <v>4.9320000000000006E-3</v>
-      </c>
-      <c r="F35" t="s">
-        <v>54</v>
-      </c>
-      <c r="Q35" t="s">
-        <v>55</v>
+        <v>30</v>
+      </c>
+      <c r="E35" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="36" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A36" t="s">
-        <v>72</v>
-      </c>
-      <c r="B36" t="s">
-        <v>28</v>
+        <v>85</v>
       </c>
       <c r="C36">
-        <v>0.02</v>
+        <v>1</v>
       </c>
       <c r="D36" s="1">
-        <v>0.55000000000000004</v>
+        <v>2.95</v>
       </c>
       <c r="E36" s="1">
-        <f t="shared" si="2"/>
-        <v>1.5070000000000004E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.95</v>
       </c>
       <c r="F36" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q36" t="s">
-        <v>55</v>
+        <v>86</v>
       </c>
     </row>
     <row r="37" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A37" t="s">
-        <v>66</v>
-      </c>
-      <c r="B37" t="s">
-        <v>67</v>
+        <v>32</v>
       </c>
       <c r="C37">
         <v>0.01</v>
       </c>
       <c r="D37" s="1">
-        <v>0.14000000000000001</v>
+        <v>6.94</v>
       </c>
       <c r="E37" s="1">
-        <f t="shared" si="2"/>
-        <v>1.9180000000000004E-3</v>
+        <f t="shared" si="4"/>
+        <v>6.9400000000000003E-2</v>
       </c>
       <c r="F37" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q37" t="s">
-        <v>47</v>
+        <v>31</v>
       </c>
     </row>
     <row r="38" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A38" t="s">
-        <v>69</v>
-      </c>
-      <c r="B38" t="s">
-        <v>70</v>
-      </c>
-      <c r="C38">
-        <v>0.12</v>
-      </c>
-      <c r="D38" s="1">
-        <v>0.52</v>
-      </c>
-      <c r="E38" s="1">
-        <f t="shared" si="2"/>
-        <v>8.5488000000000008E-2</v>
-      </c>
-      <c r="F38" t="s">
-        <v>71</v>
-      </c>
-      <c r="Q38" t="s">
-        <v>112</v>
+        <v>18</v>
+      </c>
+      <c r="E38" s="1" t="str">
+        <f t="shared" si="4"/>
+        <v/>
       </c>
     </row>
     <row r="39" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A39" t="s">
-        <v>77</v>
+        <v>117</v>
+      </c>
+      <c r="B39" t="s">
+        <v>118</v>
       </c>
       <c r="C39">
-        <v>1</v>
+        <v>0.02</v>
       </c>
       <c r="D39" s="1">
-        <v>0.23</v>
+        <v>0.52</v>
       </c>
       <c r="E39" s="1">
-        <f t="shared" si="2"/>
-        <v>0.23</v>
+        <f t="shared" si="4"/>
+        <v>1.4248000000000002E-2</v>
       </c>
       <c r="F39" t="s">
-        <v>78</v>
+        <v>119</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>45</v>
       </c>
     </row>
     <row r="40" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A40" t="s">
-        <v>38</v>
+        <v>120</v>
       </c>
       <c r="B40" t="s">
-        <v>39</v>
+        <v>121</v>
       </c>
       <c r="C40">
-        <v>0.08</v>
+        <v>0.02</v>
       </c>
       <c r="D40" s="1">
-        <v>0.52</v>
+        <v>0.74</v>
       </c>
       <c r="E40" s="1">
-        <f t="shared" si="2"/>
-        <v>5.6992000000000008E-2</v>
+        <f t="shared" si="4"/>
+        <v>2.0276000000000002E-2</v>
       </c>
       <c r="F40" t="s">
-        <v>60</v>
+        <v>122</v>
       </c>
       <c r="Q40" t="s">
-        <v>79</v>
+        <v>45</v>
       </c>
     </row>
     <row r="41" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A41" t="s">
-        <v>82</v>
+        <v>123</v>
+      </c>
+      <c r="B41" t="s">
+        <v>124</v>
       </c>
       <c r="C41">
-        <v>0.8</v>
+        <v>0.02</v>
       </c>
       <c r="D41" s="1">
-        <v>0.39</v>
+        <v>0.55000000000000004</v>
       </c>
       <c r="E41" s="1">
-        <f t="shared" si="2"/>
-        <v>0.4274400000000001</v>
+        <f t="shared" si="4"/>
+        <v>1.5070000000000004E-2</v>
       </c>
       <c r="F41" t="s">
-        <v>81</v>
+        <v>125</v>
       </c>
       <c r="Q41" t="s">
-        <v>123</v>
+        <v>45</v>
       </c>
     </row>
     <row r="42" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A42" t="s">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="E42" s="1" t="str">
-        <f t="shared" si="2"/>
+        <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
     <row r="43" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A43" t="s">
-        <v>29</v>
-      </c>
-      <c r="C43">
-        <v>1</v>
-      </c>
-      <c r="D43" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="E43" s="1">
-        <f t="shared" si="2"/>
-        <v>0.91790000000000016</v>
-      </c>
-      <c r="F43" t="s">
-        <v>46</v>
+        <v>93</v>
+      </c>
+      <c r="B43" t="s">
+        <v>15</v>
+      </c>
+      <c r="C43" t="s">
+        <v>66</v>
       </c>
     </row>
     <row r="44" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A44" t="s">
-        <v>31</v>
+        <v>44</v>
+      </c>
+      <c r="B44" t="s">
+        <v>16</v>
       </c>
       <c r="C44">
-        <v>0.1</v>
+        <v>0.3</v>
       </c>
       <c r="D44" s="1">
-        <v>0.51</v>
+        <v>0.15</v>
       </c>
       <c r="E44" s="1">
-        <f t="shared" si="2"/>
-        <v>6.9870000000000015E-2</v>
+        <f>IF(COUNT(C44:D44)=2,D44*C44*IF(ISNUMBER(SEARCH("lcsc", F44)), U$2, 1),"")</f>
+        <v>6.1650000000000003E-2</v>
       </c>
       <c r="F44" t="s">
-        <v>57</v>
+        <v>43</v>
       </c>
       <c r="Q44" t="s">
-        <v>58</v>
+        <v>138</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A45" t="s">
-        <v>32</v>
+        <v>61</v>
       </c>
       <c r="B45" t="s">
-        <v>33</v>
+        <v>17</v>
       </c>
       <c r="C45">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="D45" s="1">
-        <v>0.31</v>
+        <v>0.71</v>
       </c>
       <c r="E45" s="1">
-        <f t="shared" si="2"/>
-        <v>2.5482000000000001E-2</v>
+        <f>IF(COUNT(C45:D45)=2,D45*C45*IF(ISNUMBER(SEARCH("lcsc", F45)), U$2, 1),"")</f>
+        <v>1.9453999999999999E-2</v>
       </c>
       <c r="F45" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
       <c r="Q45" t="s">
-        <v>62</v>
+        <v>52</v>
       </c>
     </row>
     <row r="46" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A46" t="s">
-        <v>38</v>
+        <v>96</v>
       </c>
       <c r="B46" t="s">
-        <v>39</v>
+        <v>19</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
-      </c>
-      <c r="E46" s="1" t="str">
-        <f t="shared" si="2"/>
-        <v/>
+        <v>35</v>
       </c>
     </row>
     <row r="47" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A47" t="s">
+        <v>58</v>
+      </c>
+      <c r="B47" t="s">
+        <v>24</v>
+      </c>
+      <c r="C47">
+        <v>0.02</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E47" s="1">
+        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
+        <v>1.5070000000000004E-2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>53</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>136</v>
+      </c>
+      <c r="B48" t="s">
+        <v>54</v>
+      </c>
+      <c r="C48">
+        <v>0.02</v>
+      </c>
+      <c r="D48" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="E48" s="1">
+        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
+        <v>1.4796000000000002E-2</v>
+      </c>
+      <c r="F48" t="s">
+        <v>137</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>55</v>
+      </c>
+      <c r="B49" t="s">
+        <v>56</v>
+      </c>
+      <c r="C49" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
         <v>63</v>
       </c>
-      <c r="B47" t="str">
+      <c r="C50">
+        <v>1</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E50" s="1">
+        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
+        <v>0.23</v>
+      </c>
+      <c r="F50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>33</v>
+      </c>
+      <c r="B51" t="s">
+        <v>34</v>
+      </c>
+      <c r="C51">
+        <v>0.08</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="E51" s="1">
+        <f>IF(COUNT(C51:D51)=2,D51*C51*IF(ISNUMBER(SEARCH("lcsc", F51)), U$2, 1),"")</f>
+        <v>5.6992000000000008E-2</v>
+      </c>
+      <c r="F51" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>68</v>
+      </c>
+      <c r="C52">
+        <v>1.2</v>
+      </c>
+      <c r="D52" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="E52" s="1">
+        <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
+        <v>0.64116000000000006</v>
+      </c>
+      <c r="F52" t="s">
+        <v>67</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>128</v>
+      </c>
+      <c r="E53" s="1" t="str">
+        <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>25</v>
+      </c>
+      <c r="C54">
+        <v>1</v>
+      </c>
+      <c r="D54" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E54" s="1">
+        <f>IF(COUNT(C54:D54)=2,D54*C54*IF(ISNUMBER(SEARCH("lcsc", F54)), U$2, 1),"")</f>
+        <v>0.91790000000000016</v>
+      </c>
+      <c r="F54" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>27</v>
+      </c>
+      <c r="B55" t="s">
+        <v>28</v>
+      </c>
+      <c r="C55" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>33</v>
+      </c>
+      <c r="B56" t="s">
+        <v>34</v>
+      </c>
+      <c r="C56" t="s">
+        <v>66</v>
+      </c>
+      <c r="E56" s="1" t="str">
+        <f>IF(COUNT(C56:D56)=2,D56*C56*IF(ISNUMBER(SEARCH("lcsc", F56)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>51</v>
+      </c>
+      <c r="B57" t="str">
         <f>TEXT("10", "#")</f>
         <v>10</v>
       </c>
-      <c r="C47">
-        <v>0.2</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="E47" s="1">
-        <f t="shared" si="2"/>
-        <v>0.03</v>
-      </c>
-      <c r="F47" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>51</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>56</v>
-      </c>
-      <c r="B48" t="s">
-        <v>19</v>
-      </c>
-      <c r="C48" t="s">
-        <v>40</v>
-      </c>
-      <c r="E48" s="1" t="str">
-        <f t="shared" si="2"/>
+      <c r="C57">
+        <v>0.02</v>
+      </c>
+      <c r="D57" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="E57" s="1">
+        <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
+        <v>1.0686000000000001E-2</v>
+      </c>
+      <c r="F57" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>93</v>
+      </c>
+      <c r="B58" t="s">
+        <v>15</v>
+      </c>
+      <c r="C58" t="s">
+        <v>35</v>
+      </c>
+      <c r="E58" s="1" t="str">
+        <f>IF(COUNT(C58:D58)=2,D58*C58*IF(ISNUMBER(SEARCH("lcsc", F58)), U$2, 1),"")</f>
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>73</v>
-      </c>
-      <c r="C49">
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>59</v>
+      </c>
+      <c r="C60">
         <v>2</v>
       </c>
-      <c r="D49" s="1">
+      <c r="D60" s="1">
         <v>0.68</v>
       </c>
-      <c r="E49" s="1">
-        <f t="shared" si="2"/>
+      <c r="E60" s="1">
+        <f t="shared" ref="E60:E65" si="5">IF(COUNT(C60:D60)=2,D60*C60*IF(ISNUMBER(SEARCH("lcsc", F60)), U$2, 1),"")</f>
         <v>1.36</v>
       </c>
-      <c r="F49" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>41</v>
-      </c>
-      <c r="E50" s="1" t="str">
-        <f t="shared" si="2"/>
+      <c r="F60" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>130</v>
+      </c>
+      <c r="C61">
+        <v>2</v>
+      </c>
+      <c r="D61" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="E61" s="1">
+        <f t="shared" si="5"/>
+        <v>1.62</v>
+      </c>
+      <c r="F61" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="62" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A62" t="s">
+        <v>36</v>
+      </c>
+      <c r="E62" s="1" t="str">
+        <f t="shared" si="5"/>
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>43</v>
-      </c>
-      <c r="C51">
-        <v>2</v>
-      </c>
-      <c r="D51" s="1">
+    <row r="63" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A63" t="s">
+        <v>132</v>
+      </c>
+      <c r="C63">
+        <v>1</v>
+      </c>
+      <c r="D63" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="E63" s="1">
+        <f t="shared" si="5"/>
+        <v>0.64390000000000003</v>
+      </c>
+      <c r="F63" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="64" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A64" t="s">
+        <v>38</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="D64" s="1">
         <v>0.5</v>
       </c>
-      <c r="E51" s="1">
-        <f t="shared" si="2"/>
-        <v>1.37</v>
-      </c>
-      <c r="F51" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>42</v>
-      </c>
-      <c r="C52">
-        <v>2</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E52" s="1">
-        <f t="shared" si="2"/>
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="F52" t="s">
-        <v>83</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D53" s="1" t="s">
-        <v>34</v>
-      </c>
-      <c r="E53" s="1">
-        <f>SUM(E2:E52)</f>
-        <v>82.989503000000013</v>
+      <c r="E64" s="1">
+        <f t="shared" si="5"/>
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="F64" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="A65" t="s">
+        <v>37</v>
+      </c>
+      <c r="C65">
+        <v>0.4</v>
+      </c>
+      <c r="D65" s="1">
+        <v>1.27</v>
+      </c>
+      <c r="E65" s="1">
+        <f t="shared" si="5"/>
+        <v>0.69596000000000002</v>
+      </c>
+      <c r="F65" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="D66" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="E66" s="1">
+        <f>SUM(E2:E65)</f>
+        <v>100.083777</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4796AFC8-5DC9-4F86-83AE-D524F6B81D9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54266DE3-0BC9-4B88-9EC3-553AA017F7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="141">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -455,7 +455,10 @@
     <t>*3 out of 10</t>
   </si>
   <si>
-    <t>*6 out of 5</t>
+    <t>*4 out of 5</t>
+  </si>
+  <si>
+    <t>*8 out of 100</t>
   </si>
 </sst>
 </file>
@@ -1775,14 +1778,14 @@
         <v>68</v>
       </c>
       <c r="C52">
-        <v>1.2</v>
+        <v>0.8</v>
       </c>
       <c r="D52" s="1">
         <v>0.39</v>
       </c>
       <c r="E52" s="1">
         <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
-        <v>0.64116000000000006</v>
+        <v>0.4274400000000001</v>
       </c>
       <c r="F52" t="s">
         <v>67</v>
@@ -1853,20 +1856,20 @@
         <v>10</v>
       </c>
       <c r="C57">
-        <v>0.02</v>
+        <v>0.08</v>
       </c>
       <c r="D57" s="1">
         <v>0.39</v>
       </c>
       <c r="E57" s="1">
         <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
-        <v>1.0686000000000001E-2</v>
+        <v>4.2744000000000004E-2</v>
       </c>
       <c r="F57" t="s">
         <v>135</v>
       </c>
       <c r="Q57" t="s">
-        <v>52</v>
+        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
@@ -1994,7 +1997,7 @@
       </c>
       <c r="E66" s="1">
         <f>SUM(E2:E65)</f>
-        <v>100.083777</v>
+        <v>99.902114999999995</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{54266DE3-0BC9-4B88-9EC3-553AA017F7CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02595036-1A80-474C-9C7F-4D3D47CE0D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -443,9 +443,6 @@
     <t>https://www.lcsc.com/product-detail/C189895.html</t>
   </si>
   <si>
-    <t>https://www.lcsc.com/product-detail/C109318.html</t>
-  </si>
-  <si>
     <t>RT0603FRE07390KL</t>
   </si>
   <si>
@@ -458,7 +455,10 @@
     <t>*4 out of 5</t>
   </si>
   <si>
-    <t>*8 out of 100</t>
+    <t>https://www.lcsc.com/product-detail/C861082.html</t>
+  </si>
+  <si>
+    <t>*8 out of 20</t>
   </si>
 </sst>
 </file>
@@ -1634,7 +1634,7 @@
         <v>43</v>
       </c>
       <c r="Q44" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
@@ -1698,7 +1698,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -1714,7 +1714,7 @@
         <v>1.4796000000000002E-2</v>
       </c>
       <c r="F48" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="Q48" t="s">
         <v>45</v>
@@ -1791,7 +1791,7 @@
         <v>67</v>
       </c>
       <c r="Q52" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
@@ -1856,17 +1856,17 @@
         <v>10</v>
       </c>
       <c r="C57">
-        <v>0.08</v>
+        <v>0.4</v>
       </c>
       <c r="D57" s="1">
-        <v>0.39</v>
+        <v>0.94</v>
       </c>
       <c r="E57" s="1">
         <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
-        <v>4.2744000000000004E-2</v>
+        <v>0.51512000000000002</v>
       </c>
       <c r="F57" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="Q57" t="s">
         <v>140</v>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="E66" s="1">
         <f>SUM(E2:E65)</f>
-        <v>99.902114999999995</v>
+        <v>100.37449099999999</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{02595036-1A80-474C-9C7F-4D3D47CE0D8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40BFCCB-881D-491D-95A7-885F26CD4059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -416,9 +416,6 @@
     <t>https://www.lcsc.com/product-detail/C18438.html</t>
   </si>
   <si>
-    <t>*12 out of 50</t>
-  </si>
-  <si>
     <t>*2 out of 50</t>
   </si>
   <si>
@@ -459,6 +456,9 @@
   </si>
   <si>
     <t>*8 out of 20</t>
+  </si>
+  <si>
+    <t>*16 out of 50</t>
   </si>
 </sst>
 </file>
@@ -951,20 +951,20 @@
         <v>15</v>
       </c>
       <c r="C7">
-        <v>0.24</v>
+        <v>0.32</v>
       </c>
       <c r="D7" s="1">
         <v>0.33</v>
       </c>
       <c r="E7" s="1">
         <f t="shared" si="1"/>
-        <v>0.10850400000000002</v>
+        <v>0.14467200000000002</v>
       </c>
       <c r="F7" t="s">
         <v>94</v>
       </c>
       <c r="Q7" t="s">
-        <v>126</v>
+        <v>140</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
@@ -1380,7 +1380,7 @@
         <v>57</v>
       </c>
       <c r="Q29" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
@@ -1634,7 +1634,7 @@
         <v>43</v>
       </c>
       <c r="Q44" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="45" spans="1:17" x14ac:dyDescent="0.35">
@@ -1698,7 +1698,7 @@
     </row>
     <row r="48" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A48" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B48" t="s">
         <v>54</v>
@@ -1714,7 +1714,7 @@
         <v>1.4796000000000002E-2</v>
       </c>
       <c r="F48" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q48" t="s">
         <v>45</v>
@@ -1791,12 +1791,12 @@
         <v>67</v>
       </c>
       <c r="Q52" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="53" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A53" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="E53" s="1" t="str">
         <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
@@ -1866,10 +1866,10 @@
         <v>0.51512000000000002</v>
       </c>
       <c r="F57" t="s">
+        <v>138</v>
+      </c>
+      <c r="Q57" t="s">
         <v>139</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>140</v>
       </c>
     </row>
     <row r="58" spans="1:17" x14ac:dyDescent="0.35">
@@ -1889,7 +1889,7 @@
     </row>
     <row r="59" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A59" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="60" spans="1:17" x14ac:dyDescent="0.35">
@@ -1912,7 +1912,7 @@
     </row>
     <row r="61" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A61" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="C61">
         <v>2</v>
@@ -1925,7 +1925,7 @@
         <v>1.62</v>
       </c>
       <c r="F61" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
@@ -1939,7 +1939,7 @@
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C63">
         <v>1</v>
@@ -1952,7 +1952,7 @@
         <v>0.64390000000000003</v>
       </c>
       <c r="F63" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
@@ -1988,7 +1988,7 @@
         <v>0.69596000000000002</v>
       </c>
       <c r="F65" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.35">
@@ -1997,7 +1997,7 @@
       </c>
       <c r="E66" s="1">
         <f>SUM(E2:E65)</f>
-        <v>100.37449099999999</v>
+        <v>100.410659</v>
       </c>
     </row>
   </sheetData>

--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E40BFCCB-881D-491D-95A7-885F26CD4059}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80243CE5-BB28-45B3-B7D1-5A1DFBA0A4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="176" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="141">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -191,9 +191,6 @@
     <t>https://www.lcsc.com/product-detail/C138687.html</t>
   </si>
   <si>
-    <t>RC0603FR-0710RL</t>
-  </si>
-  <si>
     <t>*2 out of 100</t>
   </si>
   <si>
@@ -281,18 +278,6 @@
     <t>*6 out of 50</t>
   </si>
   <si>
-    <t>RC0603FR-072R2L</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C112307.html</t>
-  </si>
-  <si>
-    <t>RC0603FR-071RL</t>
-  </si>
-  <si>
-    <t>https://www.lcsc.com/product-detail/C112305.html</t>
-  </si>
-  <si>
     <t>HSB35-272725</t>
   </si>
   <si>
@@ -459,6 +444,21 @@
   </si>
   <si>
     <t>*16 out of 50</t>
+  </si>
+  <si>
+    <t>RC0603FR-070RL</t>
+  </si>
+  <si>
+    <t>https://www.lcsc.com/product-detail/C95177.html</t>
+  </si>
+  <si>
+    <t>*8 out of 100</t>
+  </si>
+  <si>
+    <t>​0</t>
+  </si>
+  <si>
+    <t>RT0603BRD0710RL</t>
   </si>
 </sst>
 </file>
@@ -494,9 +494,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -831,7 +832,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05E459BF-586A-4F4B-931A-B6F36BAD946F}">
-  <dimension ref="A1:U66"/>
+  <dimension ref="A1:U65"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="20.453125" customWidth="1"/>
@@ -850,10 +851,10 @@
         <v>2</v>
       </c>
       <c r="D1" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>77</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="F1" t="s">
         <v>3</v>
@@ -868,7 +869,7 @@
         <v/>
       </c>
       <c r="R2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="U2">
         <v>1.37</v>
@@ -876,7 +877,7 @@
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A3" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="C3">
         <v>1</v>
@@ -889,7 +890,7 @@
         <v>5.0964000000000009</v>
       </c>
       <c r="F3" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.35">
@@ -903,10 +904,10 @@
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
+        <v>68</v>
+      </c>
+      <c r="B5" t="s">
         <v>69</v>
-      </c>
-      <c r="B5" t="s">
-        <v>70</v>
       </c>
       <c r="C5">
         <v>4</v>
@@ -919,7 +920,7 @@
         <v>7.68</v>
       </c>
       <c r="F5" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.35">
@@ -945,7 +946,7 @@
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B7" t="s">
         <v>15</v>
@@ -961,15 +962,15 @@
         <v>0.14467200000000002</v>
       </c>
       <c r="F7" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="Q7" t="s">
-        <v>140</v>
+        <v>135</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>96</v>
+        <v>91</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
@@ -985,10 +986,10 @@
         <v>4.3155000000000006E-2</v>
       </c>
       <c r="F8" t="s">
-        <v>97</v>
+        <v>92</v>
       </c>
       <c r="Q8" t="s">
-        <v>98</v>
+        <v>93</v>
       </c>
     </row>
     <row r="9" spans="1:21" x14ac:dyDescent="0.35">
@@ -1002,7 +1003,7 @@
     </row>
     <row r="10" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="B10" t="s">
         <v>12</v>
@@ -1018,7 +1019,7 @@
         <v>2.92</v>
       </c>
       <c r="F10" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
     </row>
     <row r="11" spans="1:21" x14ac:dyDescent="0.35">
@@ -1044,18 +1045,18 @@
     </row>
     <row r="12" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B12" t="s">
         <v>15</v>
       </c>
       <c r="C12" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
     </row>
     <row r="13" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="E13" s="1" t="str">
         <f>IF(COUNT(C13:D13)=2,D13*C13*IF(ISNUMBER(SEARCH("lcsc", F13)), U$2, 1),"")</f>
@@ -1064,7 +1065,7 @@
     </row>
     <row r="14" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="C14">
         <v>4</v>
@@ -1077,12 +1078,12 @@
         <v>26.48</v>
       </c>
       <c r="F14" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
     </row>
     <row r="15" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C15">
         <v>2</v>
@@ -1095,15 +1096,15 @@
         <v>13.58</v>
       </c>
       <c r="F15" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
     </row>
     <row r="16" spans="1:21" x14ac:dyDescent="0.35">
       <c r="A16" t="s">
-        <v>102</v>
+        <v>97</v>
       </c>
       <c r="B16" t="s">
-        <v>103</v>
+        <v>98</v>
       </c>
       <c r="C16">
         <v>0.04</v>
@@ -1116,7 +1117,7 @@
         <v>7.124000000000001E-3</v>
       </c>
       <c r="F16" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="Q16" t="s">
         <v>42</v>
@@ -1124,10 +1125,10 @@
     </row>
     <row r="17" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A17" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="B17" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C17">
         <v>0.04</v>
@@ -1140,7 +1141,7 @@
         <v>2.4660000000000005E-2</v>
       </c>
       <c r="F17" t="s">
-        <v>107</v>
+        <v>102</v>
       </c>
       <c r="Q17" t="s">
         <v>42</v>
@@ -1167,12 +1168,12 @@
         <v>48</v>
       </c>
       <c r="Q18" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="19" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A19" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C19">
         <v>0.4</v>
@@ -1185,15 +1186,15 @@
         <v>0.38907999999999998</v>
       </c>
       <c r="F19" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="Q19" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="20" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A20" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="B20" t="str">
         <f>TEXT("100", "#")</f>
@@ -1210,21 +1211,21 @@
         <v>3.5620000000000005E-3</v>
       </c>
       <c r="F20" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="Q20" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="21" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A21" t="s">
-        <v>93</v>
+        <v>88</v>
       </c>
       <c r="B21" t="s">
         <v>15</v>
       </c>
       <c r="C21" t="s">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="E21" s="1" t="str">
         <f t="shared" si="2"/>
@@ -1233,90 +1234,79 @@
     </row>
     <row r="22" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A22" t="s">
-        <v>81</v>
-      </c>
-      <c r="B22" t="str">
-        <f>TEXT(2.2, "#.#")</f>
-        <v>2.2</v>
+        <v>136</v>
+      </c>
+      <c r="B22" s="2" t="s">
+        <v>139</v>
       </c>
       <c r="C22">
-        <v>0.04</v>
+        <v>0.08</v>
       </c>
       <c r="D22" s="1">
-        <v>0.37</v>
+        <v>0.12</v>
       </c>
       <c r="E22" s="1">
-        <f>IF(COUNT(C22:D22)=2,D22*C22*IF(ISNUMBER(SEARCH("lcsc", F22)), U$2, 1),"")</f>
-        <v>2.0276000000000002E-2</v>
+        <f t="shared" ref="E22:E41" si="3">IF(COUNT(C22:D22)=2,D22*C22*IF(ISNUMBER(SEARCH("lcsc", F22)), U$2, 1),"")</f>
+        <v>1.3152E-2</v>
       </c>
       <c r="F22" t="s">
-        <v>82</v>
+        <v>137</v>
       </c>
       <c r="Q22" t="s">
-        <v>42</v>
+        <v>138</v>
       </c>
     </row>
     <row r="23" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A23" t="s">
-        <v>83</v>
-      </c>
-      <c r="B23" t="str">
-        <f>TEXT(1, "#")</f>
-        <v>1</v>
-      </c>
-      <c r="C23">
-        <v>0.04</v>
-      </c>
-      <c r="D23" s="1">
-        <v>0.35</v>
-      </c>
-      <c r="E23" s="1">
-        <f>IF(COUNT(C23:D23)=2,D23*C23*IF(ISNUMBER(SEARCH("lcsc", F23)), U$2, 1),"")</f>
-        <v>1.9179999999999999E-2</v>
-      </c>
-      <c r="F23" t="s">
-        <v>84</v>
-      </c>
-      <c r="Q23" t="s">
-        <v>42</v>
+        <v>107</v>
+      </c>
+      <c r="E23" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
       </c>
     </row>
     <row r="24" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A24" t="s">
-        <v>112</v>
-      </c>
-      <c r="E24" s="1" t="str">
-        <f t="shared" ref="E24:E27" si="3">IF(COUNT(C24:D24)=2,D24*C24*IF(ISNUMBER(SEARCH("lcsc", F24)), U$2, 1),"")</f>
-        <v/>
+        <v>108</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="D24" s="1">
+        <v>0.75</v>
+      </c>
+      <c r="E24" s="1">
+        <f t="shared" si="3"/>
+        <v>0.75</v>
+      </c>
+      <c r="F24" t="s">
+        <v>109</v>
       </c>
     </row>
     <row r="25" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A25" t="s">
-        <v>113</v>
-      </c>
-      <c r="C25">
-        <v>1</v>
-      </c>
-      <c r="D25" s="1">
-        <v>0.75</v>
-      </c>
-      <c r="E25" s="1">
+        <v>27</v>
+      </c>
+      <c r="B25" t="s">
+        <v>28</v>
+      </c>
+      <c r="C25" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="1" t="str">
         <f t="shared" si="3"/>
-        <v>0.75</v>
-      </c>
-      <c r="F25" t="s">
-        <v>114</v>
+        <v/>
       </c>
     </row>
     <row r="26" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A26" t="s">
-        <v>27</v>
+        <v>7</v>
       </c>
       <c r="B26" t="s">
-        <v>28</v>
+        <v>13</v>
       </c>
       <c r="C26" t="s">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="E26" s="1" t="str">
         <f t="shared" si="3"/>
@@ -1325,682 +1315,668 @@
     </row>
     <row r="27" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A27" t="s">
-        <v>7</v>
-      </c>
-      <c r="B27" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" t="s">
-        <v>35</v>
-      </c>
-      <c r="E27" s="1" t="str">
+        <v>26</v>
+      </c>
+      <c r="C27">
+        <v>0.1</v>
+      </c>
+      <c r="D27" s="1">
+        <v>0.51</v>
+      </c>
+      <c r="E27" s="1">
+        <f t="shared" si="3"/>
+        <v>6.9870000000000015E-2</v>
+      </c>
+      <c r="F27" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A28" t="s">
+        <v>54</v>
+      </c>
+      <c r="B28" t="s">
+        <v>55</v>
+      </c>
+      <c r="C28">
+        <v>0.04</v>
+      </c>
+      <c r="D28" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="E28" s="1">
+        <f t="shared" si="3"/>
+        <v>2.8496000000000004E-2</v>
+      </c>
+      <c r="F28" t="s">
+        <v>56</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A29" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="1" t="str">
         <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
-        <v>26</v>
-      </c>
-      <c r="C28">
-        <v>0.1</v>
-      </c>
-      <c r="D28" s="1">
-        <v>0.51</v>
-      </c>
-      <c r="E28" s="1">
-        <f t="shared" ref="E28:E42" si="4">IF(COUNT(C28:D28)=2,D28*C28*IF(ISNUMBER(SEARCH("lcsc", F28)), U$2, 1),"")</f>
-        <v>6.9870000000000015E-2</v>
-      </c>
-      <c r="F28" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q28" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A29" t="s">
-        <v>55</v>
-      </c>
-      <c r="B29" t="s">
-        <v>56</v>
-      </c>
-      <c r="C29">
-        <v>0.04</v>
-      </c>
-      <c r="D29" s="1">
-        <v>0.52</v>
-      </c>
-      <c r="E29" s="1">
-        <f t="shared" si="4"/>
-        <v>2.8496000000000004E-2</v>
-      </c>
-      <c r="F29" t="s">
-        <v>57</v>
-      </c>
-      <c r="Q29" t="s">
-        <v>126</v>
-      </c>
-    </row>
     <row r="30" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A30" t="s">
-        <v>8</v>
-      </c>
-      <c r="E30" s="1" t="str">
+        <v>110</v>
+      </c>
+      <c r="B30" t="s">
+        <v>14</v>
+      </c>
+      <c r="C30">
+        <v>2</v>
+      </c>
+      <c r="D30" s="1">
+        <v>2.99</v>
+      </c>
+      <c r="E30" s="1">
+        <f t="shared" si="3"/>
+        <v>8.1926000000000005</v>
+      </c>
+      <c r="F30" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A31" t="s">
+        <v>21</v>
+      </c>
+      <c r="E31" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A32" t="s">
+        <v>71</v>
+      </c>
+      <c r="B32" t="s">
+        <v>72</v>
+      </c>
+      <c r="C32">
+        <v>0.4</v>
+      </c>
+      <c r="D32" s="1">
+        <v>1.35</v>
+      </c>
+      <c r="E32" s="1">
+        <f t="shared" si="3"/>
+        <v>0.73980000000000012</v>
+      </c>
+      <c r="F32" t="s">
+        <v>73</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A33" t="s">
+        <v>22</v>
+      </c>
+      <c r="B33" t="s">
+        <v>23</v>
+      </c>
+      <c r="C33">
+        <v>4</v>
+      </c>
+      <c r="D33" s="1">
+        <v>3.13</v>
+      </c>
+      <c r="E33" s="1">
+        <f t="shared" si="3"/>
+        <v>17.1524</v>
+      </c>
+      <c r="F33" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A34" t="s">
+        <v>30</v>
+      </c>
+      <c r="E34" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A35" t="s">
+        <v>80</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="D35" s="1">
+        <v>2.95</v>
+      </c>
+      <c r="E35" s="1">
+        <f t="shared" si="3"/>
+        <v>2.95</v>
+      </c>
+      <c r="F35" t="s">
+        <v>81</v>
+      </c>
+    </row>
+    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A36" t="s">
+        <v>32</v>
+      </c>
+      <c r="C36">
+        <v>0.01</v>
+      </c>
+      <c r="D36" s="1">
+        <v>6.94</v>
+      </c>
+      <c r="E36" s="1">
+        <f t="shared" si="3"/>
+        <v>6.9400000000000003E-2</v>
+      </c>
+      <c r="F36" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A37" t="s">
+        <v>18</v>
+      </c>
+      <c r="E37" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A38" t="s">
+        <v>112</v>
+      </c>
+      <c r="B38" t="s">
+        <v>113</v>
+      </c>
+      <c r="C38">
+        <v>0.02</v>
+      </c>
+      <c r="D38" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="E38" s="1">
+        <f t="shared" si="3"/>
+        <v>1.4248000000000002E-2</v>
+      </c>
+      <c r="F38" t="s">
+        <v>114</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A39" t="s">
+        <v>115</v>
+      </c>
+      <c r="B39" t="s">
+        <v>116</v>
+      </c>
+      <c r="C39">
+        <v>0.02</v>
+      </c>
+      <c r="D39" s="1">
+        <v>0.74</v>
+      </c>
+      <c r="E39" s="1">
+        <f t="shared" si="3"/>
+        <v>2.0276000000000002E-2</v>
+      </c>
+      <c r="F39" t="s">
+        <v>117</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A40" t="s">
+        <v>118</v>
+      </c>
+      <c r="B40" t="s">
+        <v>119</v>
+      </c>
+      <c r="C40">
+        <v>0.02</v>
+      </c>
+      <c r="D40" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E40" s="1">
+        <f t="shared" si="3"/>
+        <v>1.5070000000000004E-2</v>
+      </c>
+      <c r="F40" t="s">
+        <v>120</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A41" t="s">
+        <v>20</v>
+      </c>
+      <c r="E41" s="1" t="str">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+    </row>
+    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A42" t="s">
+        <v>88</v>
+      </c>
+      <c r="B42" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A43" t="s">
+        <v>44</v>
+      </c>
+      <c r="B43" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43">
+        <v>0.3</v>
+      </c>
+      <c r="D43" s="1">
+        <v>0.15</v>
+      </c>
+      <c r="E43" s="1">
+        <f>IF(COUNT(C43:D43)=2,D43*C43*IF(ISNUMBER(SEARCH("lcsc", F43)), U$2, 1),"")</f>
+        <v>6.1650000000000003E-2</v>
+      </c>
+      <c r="F43" t="s">
+        <v>43</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A44" t="s">
+        <v>60</v>
+      </c>
+      <c r="B44" t="s">
+        <v>17</v>
+      </c>
+      <c r="C44">
+        <v>0.02</v>
+      </c>
+      <c r="D44" s="1">
+        <v>0.71</v>
+      </c>
+      <c r="E44" s="1">
+        <f>IF(COUNT(C44:D44)=2,D44*C44*IF(ISNUMBER(SEARCH("lcsc", F44)), U$2, 1),"")</f>
+        <v>1.9453999999999999E-2</v>
+      </c>
+      <c r="F44" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A45" t="s">
+        <v>91</v>
+      </c>
+      <c r="B45" t="s">
+        <v>19</v>
+      </c>
+      <c r="C45" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A46" t="s">
+        <v>57</v>
+      </c>
+      <c r="B46" t="s">
+        <v>24</v>
+      </c>
+      <c r="C46">
+        <v>0.02</v>
+      </c>
+      <c r="D46" s="1">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="E46" s="1">
+        <f>IF(COUNT(C46:D46)=2,D46*C46*IF(ISNUMBER(SEARCH("lcsc", F46)), U$2, 1),"")</f>
+        <v>1.5070000000000004E-2</v>
+      </c>
+      <c r="F46" t="s">
+        <v>52</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A47" t="s">
+        <v>129</v>
+      </c>
+      <c r="B47" t="s">
+        <v>53</v>
+      </c>
+      <c r="C47">
+        <v>0.02</v>
+      </c>
+      <c r="D47" s="1">
+        <v>0.54</v>
+      </c>
+      <c r="E47" s="1">
+        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
+        <v>1.4796000000000002E-2</v>
+      </c>
+      <c r="F47" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A48" t="s">
+        <v>54</v>
+      </c>
+      <c r="B48" t="s">
+        <v>55</v>
+      </c>
+      <c r="C48" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A49" t="s">
+        <v>62</v>
+      </c>
+      <c r="C49">
+        <v>1</v>
+      </c>
+      <c r="D49" s="1">
+        <v>0.23</v>
+      </c>
+      <c r="E49" s="1">
+        <f>IF(COUNT(C49:D49)=2,D49*C49*IF(ISNUMBER(SEARCH("lcsc", F49)), U$2, 1),"")</f>
+        <v>0.23</v>
+      </c>
+      <c r="F49" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A50" t="s">
+        <v>33</v>
+      </c>
+      <c r="B50" t="s">
+        <v>34</v>
+      </c>
+      <c r="C50">
+        <v>0.08</v>
+      </c>
+      <c r="D50" s="1">
+        <v>0.52</v>
+      </c>
+      <c r="E50" s="1">
+        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
+        <v>5.6992000000000008E-2</v>
+      </c>
+      <c r="F50" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A51" t="s">
+        <v>67</v>
+      </c>
+      <c r="C51">
+        <v>0.8</v>
+      </c>
+      <c r="D51" s="1">
+        <v>0.39</v>
+      </c>
+      <c r="E51" s="1">
+        <f>IF(COUNT(C51:D51)=2,D51*C51*IF(ISNUMBER(SEARCH("lcsc", F51)), U$2, 1),"")</f>
+        <v>0.4274400000000001</v>
+      </c>
+      <c r="F51" t="s">
+        <v>66</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A52" t="s">
+        <v>122</v>
+      </c>
+      <c r="E52" s="1" t="str">
+        <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A53" t="s">
+        <v>25</v>
+      </c>
+      <c r="C53">
+        <v>1</v>
+      </c>
+      <c r="D53" s="1">
+        <v>0.67</v>
+      </c>
+      <c r="E53" s="1">
+        <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
+        <v>0.91790000000000016</v>
+      </c>
+      <c r="F53" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A54" t="s">
+        <v>27</v>
+      </c>
+      <c r="B54" t="s">
+        <v>28</v>
+      </c>
+      <c r="C54" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A55" t="s">
+        <v>33</v>
+      </c>
+      <c r="B55" t="s">
+        <v>34</v>
+      </c>
+      <c r="C55" t="s">
+        <v>65</v>
+      </c>
+      <c r="E55" s="1" t="str">
+        <f>IF(COUNT(C55:D55)=2,D55*C55*IF(ISNUMBER(SEARCH("lcsc", F55)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A56" t="s">
+        <v>140</v>
+      </c>
+      <c r="B56" t="str">
+        <f>TEXT("10", "#")</f>
+        <v>10</v>
+      </c>
+      <c r="C56">
+        <v>0.4</v>
+      </c>
+      <c r="D56" s="1">
+        <v>0.94</v>
+      </c>
+      <c r="E56" s="1">
+        <f>IF(COUNT(C56:D56)=2,D56*C56*IF(ISNUMBER(SEARCH("lcsc", F56)), U$2, 1),"")</f>
+        <v>0.51512000000000002</v>
+      </c>
+      <c r="F56" t="s">
+        <v>133</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>134</v>
+      </c>
+    </row>
+    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A57" t="s">
+        <v>88</v>
+      </c>
+      <c r="B57" t="s">
+        <v>15</v>
+      </c>
+      <c r="C57" t="s">
+        <v>35</v>
+      </c>
+      <c r="E57" s="1" t="str">
+        <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A58" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C59">
+        <v>2</v>
+      </c>
+      <c r="D59" s="1">
+        <v>0.68</v>
+      </c>
+      <c r="E59" s="1">
+        <f t="shared" ref="E59:E64" si="4">IF(COUNT(C59:D59)=2,D59*C59*IF(ISNUMBER(SEARCH("lcsc", F59)), U$2, 1),"")</f>
+        <v>1.36</v>
+      </c>
+      <c r="F59" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A60" t="s">
+        <v>124</v>
+      </c>
+      <c r="C60">
+        <v>2</v>
+      </c>
+      <c r="D60" s="1">
+        <v>0.81</v>
+      </c>
+      <c r="E60" s="1">
+        <f t="shared" si="4"/>
+        <v>1.62</v>
+      </c>
+      <c r="F60" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
+      <c r="A61" t="s">
+        <v>36</v>
+      </c>
+      <c r="E61" s="1" t="str">
         <f t="shared" si="4"/>
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A31" t="s">
-        <v>115</v>
-      </c>
-      <c r="B31" t="s">
-        <v>14</v>
-      </c>
-      <c r="C31">
-        <v>2</v>
-      </c>
-      <c r="D31" s="1">
-        <v>2.99</v>
-      </c>
-      <c r="E31" s="1">
-        <f t="shared" si="4"/>
-        <v>8.1926000000000005</v>
-      </c>
-      <c r="F31" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="32" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A32" t="s">
-        <v>21</v>
-      </c>
-      <c r="E32" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="33" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
-        <v>72</v>
-      </c>
-      <c r="B33" t="s">
-        <v>73</v>
-      </c>
-      <c r="C33">
-        <v>0.4</v>
-      </c>
-      <c r="D33" s="1">
-        <v>1.35</v>
-      </c>
-      <c r="E33" s="1">
-        <f t="shared" si="4"/>
-        <v>0.73980000000000012</v>
-      </c>
-      <c r="F33" t="s">
-        <v>74</v>
-      </c>
-      <c r="Q33" t="s">
-        <v>75</v>
-      </c>
-    </row>
-    <row r="34" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A34" t="s">
-        <v>22</v>
-      </c>
-      <c r="B34" t="s">
-        <v>23</v>
-      </c>
-      <c r="C34">
-        <v>4</v>
-      </c>
-      <c r="D34" s="1">
-        <v>3.13</v>
-      </c>
-      <c r="E34" s="1">
-        <f t="shared" si="4"/>
-        <v>17.1524</v>
-      </c>
-      <c r="F34" t="s">
-        <v>40</v>
-      </c>
-    </row>
-    <row r="35" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A35" t="s">
-        <v>30</v>
-      </c>
-      <c r="E35" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="36" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
-        <v>85</v>
-      </c>
-      <c r="C36">
-        <v>1</v>
-      </c>
-      <c r="D36" s="1">
-        <v>2.95</v>
-      </c>
-      <c r="E36" s="1">
-        <f t="shared" si="4"/>
-        <v>2.95</v>
-      </c>
-      <c r="F36" t="s">
-        <v>86</v>
-      </c>
-    </row>
-    <row r="37" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A37" t="s">
-        <v>32</v>
-      </c>
-      <c r="C37">
-        <v>0.01</v>
-      </c>
-      <c r="D37" s="1">
-        <v>6.94</v>
-      </c>
-      <c r="E37" s="1">
-        <f t="shared" si="4"/>
-        <v>6.9400000000000003E-2</v>
-      </c>
-      <c r="F37" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="38" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A38" t="s">
-        <v>18</v>
-      </c>
-      <c r="E38" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="39" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
-        <v>117</v>
-      </c>
-      <c r="B39" t="s">
-        <v>118</v>
-      </c>
-      <c r="C39">
-        <v>0.02</v>
-      </c>
-      <c r="D39" s="1">
-        <v>0.52</v>
-      </c>
-      <c r="E39" s="1">
-        <f t="shared" si="4"/>
-        <v>1.4248000000000002E-2</v>
-      </c>
-      <c r="F39" t="s">
-        <v>119</v>
-      </c>
-      <c r="Q39" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A40" t="s">
-        <v>120</v>
-      </c>
-      <c r="B40" t="s">
-        <v>121</v>
-      </c>
-      <c r="C40">
-        <v>0.02</v>
-      </c>
-      <c r="D40" s="1">
-        <v>0.74</v>
-      </c>
-      <c r="E40" s="1">
-        <f t="shared" si="4"/>
-        <v>2.0276000000000002E-2</v>
-      </c>
-      <c r="F40" t="s">
-        <v>122</v>
-      </c>
-      <c r="Q40" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="41" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A41" t="s">
-        <v>123</v>
-      </c>
-      <c r="B41" t="s">
-        <v>124</v>
-      </c>
-      <c r="C41">
-        <v>0.02</v>
-      </c>
-      <c r="D41" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E41" s="1">
-        <f t="shared" si="4"/>
-        <v>1.5070000000000004E-2</v>
-      </c>
-      <c r="F41" t="s">
-        <v>125</v>
-      </c>
-      <c r="Q41" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="42" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A42" t="s">
-        <v>20</v>
-      </c>
-      <c r="E42" s="1" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="43" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A43" t="s">
-        <v>93</v>
-      </c>
-      <c r="B43" t="s">
-        <v>15</v>
-      </c>
-      <c r="C43" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A44" t="s">
-        <v>44</v>
-      </c>
-      <c r="B44" t="s">
-        <v>16</v>
-      </c>
-      <c r="C44">
-        <v>0.3</v>
-      </c>
-      <c r="D44" s="1">
-        <v>0.15</v>
-      </c>
-      <c r="E44" s="1">
-        <f>IF(COUNT(C44:D44)=2,D44*C44*IF(ISNUMBER(SEARCH("lcsc", F44)), U$2, 1),"")</f>
-        <v>6.1650000000000003E-2</v>
-      </c>
-      <c r="F44" t="s">
-        <v>43</v>
-      </c>
-      <c r="Q44" t="s">
-        <v>136</v>
-      </c>
-    </row>
-    <row r="45" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A45" t="s">
-        <v>61</v>
-      </c>
-      <c r="B45" t="s">
-        <v>17</v>
-      </c>
-      <c r="C45">
-        <v>0.02</v>
-      </c>
-      <c r="D45" s="1">
-        <v>0.71</v>
-      </c>
-      <c r="E45" s="1">
-        <f>IF(COUNT(C45:D45)=2,D45*C45*IF(ISNUMBER(SEARCH("lcsc", F45)), U$2, 1),"")</f>
-        <v>1.9453999999999999E-2</v>
-      </c>
-      <c r="F45" t="s">
-        <v>62</v>
-      </c>
-      <c r="Q45" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="46" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A46" t="s">
-        <v>96</v>
-      </c>
-      <c r="B46" t="s">
-        <v>19</v>
-      </c>
-      <c r="C46" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="47" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A47" t="s">
-        <v>58</v>
-      </c>
-      <c r="B47" t="s">
-        <v>24</v>
-      </c>
-      <c r="C47">
-        <v>0.02</v>
-      </c>
-      <c r="D47" s="1">
-        <v>0.55000000000000004</v>
-      </c>
-      <c r="E47" s="1">
-        <f>IF(COUNT(C47:D47)=2,D47*C47*IF(ISNUMBER(SEARCH("lcsc", F47)), U$2, 1),"")</f>
-        <v>1.5070000000000004E-2</v>
-      </c>
-      <c r="F47" t="s">
-        <v>53</v>
-      </c>
-      <c r="Q47" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="48" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A48" t="s">
-        <v>134</v>
-      </c>
-      <c r="B48" t="s">
-        <v>54</v>
-      </c>
-      <c r="C48">
-        <v>0.02</v>
-      </c>
-      <c r="D48" s="1">
-        <v>0.54</v>
-      </c>
-      <c r="E48" s="1">
-        <f>IF(COUNT(C48:D48)=2,D48*C48*IF(ISNUMBER(SEARCH("lcsc", F48)), U$2, 1),"")</f>
-        <v>1.4796000000000002E-2</v>
-      </c>
-      <c r="F48" t="s">
-        <v>135</v>
-      </c>
-      <c r="Q48" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="49" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A49" t="s">
-        <v>55</v>
-      </c>
-      <c r="B49" t="s">
-        <v>56</v>
-      </c>
-      <c r="C49" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="50" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A50" t="s">
-        <v>63</v>
-      </c>
-      <c r="C50">
-        <v>1</v>
-      </c>
-      <c r="D50" s="1">
-        <v>0.23</v>
-      </c>
-      <c r="E50" s="1">
-        <f>IF(COUNT(C50:D50)=2,D50*C50*IF(ISNUMBER(SEARCH("lcsc", F50)), U$2, 1),"")</f>
-        <v>0.23</v>
-      </c>
-      <c r="F50" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="51" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A51" t="s">
-        <v>33</v>
-      </c>
-      <c r="B51" t="s">
-        <v>34</v>
-      </c>
-      <c r="C51">
-        <v>0.08</v>
-      </c>
-      <c r="D51" s="1">
-        <v>0.52</v>
-      </c>
-      <c r="E51" s="1">
-        <f>IF(COUNT(C51:D51)=2,D51*C51*IF(ISNUMBER(SEARCH("lcsc", F51)), U$2, 1),"")</f>
-        <v>5.6992000000000008E-2</v>
-      </c>
-      <c r="F51" t="s">
-        <v>49</v>
-      </c>
-      <c r="Q51" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="52" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A52" t="s">
-        <v>68</v>
-      </c>
-      <c r="C52">
-        <v>0.8</v>
-      </c>
-      <c r="D52" s="1">
-        <v>0.39</v>
-      </c>
-      <c r="E52" s="1">
-        <f>IF(COUNT(C52:D52)=2,D52*C52*IF(ISNUMBER(SEARCH("lcsc", F52)), U$2, 1),"")</f>
-        <v>0.4274400000000001</v>
-      </c>
-      <c r="F52" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q52" t="s">
-        <v>137</v>
-      </c>
-    </row>
-    <row r="53" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A53" t="s">
-        <v>127</v>
-      </c>
-      <c r="E53" s="1" t="str">
-        <f>IF(COUNT(C53:D53)=2,D53*C53*IF(ISNUMBER(SEARCH("lcsc", F53)), U$2, 1),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A54" t="s">
-        <v>25</v>
-      </c>
-      <c r="C54">
-        <v>1</v>
-      </c>
-      <c r="D54" s="1">
-        <v>0.67</v>
-      </c>
-      <c r="E54" s="1">
-        <f>IF(COUNT(C54:D54)=2,D54*C54*IF(ISNUMBER(SEARCH("lcsc", F54)), U$2, 1),"")</f>
-        <v>0.91790000000000016</v>
-      </c>
-      <c r="F54" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="55" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A55" t="s">
-        <v>27</v>
-      </c>
-      <c r="B55" t="s">
-        <v>28</v>
-      </c>
-      <c r="C55" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="56" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A56" t="s">
-        <v>33</v>
-      </c>
-      <c r="B56" t="s">
-        <v>34</v>
-      </c>
-      <c r="C56" t="s">
-        <v>66</v>
-      </c>
-      <c r="E56" s="1" t="str">
-        <f>IF(COUNT(C56:D56)=2,D56*C56*IF(ISNUMBER(SEARCH("lcsc", F56)), U$2, 1),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A57" t="s">
-        <v>51</v>
-      </c>
-      <c r="B57" t="str">
-        <f>TEXT("10", "#")</f>
-        <v>10</v>
-      </c>
-      <c r="C57">
-        <v>0.4</v>
-      </c>
-      <c r="D57" s="1">
-        <v>0.94</v>
-      </c>
-      <c r="E57" s="1">
-        <f>IF(COUNT(C57:D57)=2,D57*C57*IF(ISNUMBER(SEARCH("lcsc", F57)), U$2, 1),"")</f>
-        <v>0.51512000000000002</v>
-      </c>
-      <c r="F57" t="s">
-        <v>138</v>
-      </c>
-      <c r="Q57" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="58" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A58" t="s">
-        <v>93</v>
-      </c>
-      <c r="B58" t="s">
-        <v>15</v>
-      </c>
-      <c r="C58" t="s">
-        <v>35</v>
-      </c>
-      <c r="E58" s="1" t="str">
-        <f>IF(COUNT(C58:D58)=2,D58*C58*IF(ISNUMBER(SEARCH("lcsc", F58)), U$2, 1),"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A59" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="60" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A60" t="s">
-        <v>59</v>
-      </c>
-      <c r="C60">
-        <v>2</v>
-      </c>
-      <c r="D60" s="1">
-        <v>0.68</v>
-      </c>
-      <c r="E60" s="1">
-        <f t="shared" ref="E60:E65" si="5">IF(COUNT(C60:D60)=2,D60*C60*IF(ISNUMBER(SEARCH("lcsc", F60)), U$2, 1),"")</f>
-        <v>1.36</v>
-      </c>
-      <c r="F60" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="61" spans="1:17" x14ac:dyDescent="0.35">
-      <c r="A61" t="s">
-        <v>129</v>
-      </c>
-      <c r="C61">
-        <v>2</v>
-      </c>
-      <c r="D61" s="1">
-        <v>0.81</v>
-      </c>
-      <c r="E61" s="1">
-        <f t="shared" si="5"/>
-        <v>1.62</v>
-      </c>
-      <c r="F61" t="s">
-        <v>130</v>
-      </c>
-    </row>
     <row r="62" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A62" t="s">
-        <v>36</v>
-      </c>
-      <c r="E62" s="1" t="str">
-        <f t="shared" si="5"/>
-        <v/>
+        <v>126</v>
+      </c>
+      <c r="C62">
+        <v>1</v>
+      </c>
+      <c r="D62" s="1">
+        <v>0.47</v>
+      </c>
+      <c r="E62" s="1">
+        <f t="shared" si="4"/>
+        <v>0.64390000000000003</v>
+      </c>
+      <c r="F62" t="s">
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A63" t="s">
-        <v>131</v>
+        <v>38</v>
       </c>
       <c r="C63">
         <v>1</v>
       </c>
       <c r="D63" s="1">
-        <v>0.47</v>
+        <v>0.5</v>
       </c>
       <c r="E63" s="1">
-        <f t="shared" si="5"/>
-        <v>0.64390000000000003</v>
+        <f t="shared" si="4"/>
+        <v>0.68500000000000005</v>
       </c>
       <c r="F63" t="s">
-        <v>132</v>
+        <v>39</v>
       </c>
     </row>
     <row r="64" spans="1:17" x14ac:dyDescent="0.35">
       <c r="A64" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C64">
-        <v>1</v>
+        <v>0.4</v>
       </c>
       <c r="D64" s="1">
-        <v>0.5</v>
+        <v>1.27</v>
       </c>
       <c r="E64" s="1">
-        <f t="shared" si="5"/>
-        <v>0.68500000000000005</v>
+        <f t="shared" si="4"/>
+        <v>0.69596000000000002</v>
       </c>
       <c r="F64" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A65" t="s">
-        <v>37</v>
-      </c>
-      <c r="C65">
-        <v>0.4</v>
-      </c>
-      <c r="D65" s="1">
-        <v>1.27</v>
+        <v>128</v>
+      </c>
+    </row>
+    <row r="65" spans="4:5" x14ac:dyDescent="0.35">
+      <c r="D65" s="1" t="s">
+        <v>29</v>
       </c>
       <c r="E65" s="1">
-        <f t="shared" si="5"/>
-        <v>0.69596000000000002</v>
-      </c>
-      <c r="F65" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="D66" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="E66" s="1">
-        <f>SUM(E2:E65)</f>
-        <v>100.410659</v>
+        <f>SUM(E2:E64)</f>
+        <v>100.38435499999999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/projects/LM5143_Buck/LM5143_BOM.xlsx
+++ b/projects/LM5143_Buck/LM5143_BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Work\UWRT\MarsRoverElectricalKiCad\projects\LM5143_Buck\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80243CE5-BB28-45B3-B7D1-5A1DFBA0A4D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6E797E2D-4DDB-49E9-89BA-8A1F3DDAD13B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="13900" xr2:uid="{49714629-2E5D-47B8-A555-D616FDA96D84}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="174" uniqueCount="141">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="141">
   <si>
     <t>Capacitor In</t>
   </si>
@@ -1965,6 +1965,9 @@
       <c r="F64" t="s">
         <v>128</v>
       </c>
+      <c r="Q64" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="65" spans="4:5" x14ac:dyDescent="0.35">
       <c r="D65" s="1" t="s">
